--- a/Versão5/SIS/Ontologia_Motriz.xlsx
+++ b/Versão5/SIS/Ontologia_Motriz.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\MOTO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87A2C89-FCA8-41DA-9A06-83C3E138481A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E4C707-408B-476A-AE80-C40143AF9547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1202,163 +1202,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <font>
         <b val="0"/>
@@ -1421,6 +1265,14 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1590,6 +1442,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2032,14 +1892,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="47.140625" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="47.15234375" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2050,7 +1910,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2061,7 +1921,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2072,7 +1932,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2083,7 +1943,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2095,7 +1955,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2107,7 +1967,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2118,7 +1978,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="39" t="s">
         <v>54</v>
       </c>
@@ -2129,7 +1989,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2140,7 +2000,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2151,7 +2011,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2162,7 +2022,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2173,7 +2033,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2184,7 +2044,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2195,7 +2055,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2206,7 +2066,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2217,7 +2077,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2228,19 +2088,19 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46245.28611400463</v>
+        <v>46249.427471643517</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2251,7 +2111,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2262,7 +2122,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2273,7 +2133,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2284,7 +2144,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2295,7 +2155,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>87</v>
       </c>
@@ -2316,35 +2176,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="61" customWidth="1"/>
-    <col min="4" max="4" width="10" style="61" customWidth="1"/>
-    <col min="5" max="5" width="11" style="61" customWidth="1"/>
-    <col min="6" max="6" width="14" style="65" customWidth="1"/>
-    <col min="7" max="11" width="8" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.85546875" style="61" customWidth="1"/>
-    <col min="23" max="23" width="7.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5703125" style="66" customWidth="1"/>
-    <col min="26" max="26" width="10.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="61"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.921875" style="61" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.61328125" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.921875" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.61328125" style="61" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34" style="61" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.921875" style="61" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.4609375" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15" style="66" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.4609375" style="61" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.61328125" style="61" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="35.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="45" t="s">
         <v>92</v>
       </c>
@@ -2427,7 +2287,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>2</v>
       </c>
@@ -2519,7 +2379,7 @@
         <v>Combustion engine</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>3</v>
       </c>
@@ -2612,7 +2472,7 @@
         <v>Coupling motor</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>4</v>
       </c>
@@ -2705,7 +2565,7 @@
         <v>Belt drive motor</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>5</v>
       </c>
@@ -2798,7 +2658,7 @@
         <v>Direct drive motor</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>6</v>
       </c>
@@ -2891,7 +2751,7 @@
         <v>Engine that converts fuel into mechanical energy through combustion</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>7</v>
       </c>
@@ -2984,7 +2844,7 @@
         <v>Engine that converts fuel into mechanical energy through external combustion</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>8</v>
       </c>
@@ -3077,7 +2937,7 @@
         <v>Engine that converts fuel into mechanical energy through internal combustion</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="58">
         <v>9</v>
       </c>
@@ -3170,7 +3030,7 @@
         <v>Elevator to a few floors without carrying heavy loads</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="58">
         <v>10</v>
       </c>
@@ -3263,7 +3123,7 @@
         <v>Traction Elevator with Machine Room</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="58">
         <v>11</v>
       </c>
@@ -3356,7 +3216,7 @@
         <v>Elevator with hoisting pulley without machine room</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="58">
         <v>12</v>
       </c>
@@ -3449,7 +3309,7 @@
         <v>Lifting Platform</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="58">
         <v>13</v>
       </c>
@@ -3542,7 +3402,7 @@
         <v>Articulated lifting platform</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="58">
         <v>14</v>
       </c>
@@ -3635,7 +3495,7 @@
         <v>Basket lifting platform</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="58">
         <v>15</v>
       </c>
@@ -3728,7 +3588,7 @@
         <v>Mechanical Accessory</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="58">
         <v>16</v>
       </c>
@@ -3775,7 +3635,7 @@
         <v>Máquinas</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16:P16" si="39">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
+        <f t="shared" ref="O16" si="39">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
         <v>Máquina</v>
       </c>
       <c r="P16" s="30" t="s">
@@ -3821,7 +3681,7 @@
         <v>Machine</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="58">
         <v>17</v>
       </c>
@@ -3868,7 +3728,7 @@
         <v>Máquinas</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" ref="O17:P18" si="49">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
+        <f t="shared" ref="O17:O18" si="49">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
         <v>Bomba</v>
       </c>
       <c r="P17" s="30" t="s">
@@ -3914,7 +3774,7 @@
         <v>Pump</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="58">
         <v>18</v>
       </c>
@@ -4007,7 +3867,7 @@
         <v>Engine</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="58">
         <v>19</v>
       </c>
@@ -4054,7 +3914,7 @@
         <v>Máquinas</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" ref="O19:P19" si="59">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
+        <f t="shared" ref="O19" si="59">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
         <v>Elevador</v>
       </c>
       <c r="P19" s="30" t="s">
@@ -4100,7 +3960,7 @@
         <v>Elevator</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="58">
         <v>20</v>
       </c>
@@ -4147,7 +4007,7 @@
         <v>Máquinas</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" ref="O20:P20" si="69">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
+        <f t="shared" ref="O20" si="69">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
         <v>Escada.Rolante</v>
       </c>
       <c r="P20" s="30" t="s">
@@ -4198,57 +4058,60 @@
     <sortCondition ref="F2:F740"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
-    <cfRule type="cellIs" dxfId="40" priority="230" operator="equal">
+  <conditionalFormatting sqref="A2:B20">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
+    <cfRule type="cellIs" dxfId="25" priority="230" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F15:F1048576">
+    <cfRule type="duplicateValues" dxfId="24" priority="2009"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="39" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="duplicateValues" dxfId="38" priority="2064"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F8">
-    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F14">
-    <cfRule type="duplicateValues" dxfId="31" priority="2101"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F20">
-    <cfRule type="duplicateValues" dxfId="30" priority="138"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="29" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="28" priority="2019"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="2025"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="2026"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="2027"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2069"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2019"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2025"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X20">
-    <cfRule type="containsText" dxfId="23" priority="57" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="8" priority="57" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA14 A2:B15 A16:A20">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B20">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA2:AA14">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4256,15 +4119,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4329,7 +4192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4396,7 +4259,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4412,15 +4275,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -4443,7 +4306,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -4472,22 +4335,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="20" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4499,30 +4362,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.53515625" customWidth="1"/>
+    <col min="4" max="4" width="7.53515625" customWidth="1"/>
+    <col min="5" max="5" width="7.69140625" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="27.69140625" customWidth="1"/>
+    <col min="8" max="8" width="6.69140625" customWidth="1"/>
+    <col min="9" max="9" width="11.84375" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53515625" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="2.85546875" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.84375" customWidth="1"/>
+    <col min="14" max="14" width="7.3046875" customWidth="1"/>
+    <col min="15" max="15" width="13.84375" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.3046875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -4581,7 +4444,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4640,7 +4503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -4699,7 +4562,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -4758,7 +4621,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -4817,7 +4680,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -4876,7 +4739,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -4935,7 +4798,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -4994,7 +4857,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -5053,7 +4916,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>

--- a/Versão5/SIS/Ontologia_Motriz.xlsx
+++ b/Versão5/SIS/Ontologia_Motriz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E4C707-408B-476A-AE80-C40143AF9547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BA4B6C-E283-40CB-9145-1AE01342D846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="218">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -318,12 +318,6 @@
     <t>0-CategoriaEquivalente</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -660,6 +654,78 @@
   </si>
   <si>
     <t>"Instância de Equipamento Mecânico Motriz Identificado no projeto"</t>
+  </si>
+  <si>
+    <t>Combustion engine</t>
+  </si>
+  <si>
+    <t>Coupling motor</t>
+  </si>
+  <si>
+    <t>Belt drive motor</t>
+  </si>
+  <si>
+    <t>Direct drive motor</t>
+  </si>
+  <si>
+    <t>Engine that converts fuel into mechanical energy through combustion</t>
+  </si>
+  <si>
+    <t>Engine that converts fuel into mechanical energy through external combustion</t>
+  </si>
+  <si>
+    <t>Engine that converts fuel into mechanical energy through internal combustion</t>
+  </si>
+  <si>
+    <t>Elevator to a few floors without carrying heavy loads</t>
+  </si>
+  <si>
+    <t>Traction Elevator with Machine Room</t>
+  </si>
+  <si>
+    <t>Elevator with hoisting pulley without machine room</t>
+  </si>
+  <si>
+    <t>Lifting Platform</t>
+  </si>
+  <si>
+    <t>Articulated lifting platform</t>
+  </si>
+  <si>
+    <t>Basket lifting platform</t>
+  </si>
+  <si>
+    <t>Mechanical Accessory</t>
+  </si>
+  <si>
+    <t>Machine</t>
+  </si>
+  <si>
+    <t>Pump</t>
+  </si>
+  <si>
+    <t>Engine</t>
+  </si>
+  <si>
+    <t>Elevator</t>
+  </si>
+  <si>
+    <t>Escalator</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1973,7 @@
         <v>45</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1918,7 +1984,7 @@
         <v>47</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1926,10 +1992,10 @@
         <v>48</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1940,7 +2006,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1952,7 +2018,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1964,7 +2030,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1975,7 +2041,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1983,10 +2049,10 @@
         <v>54</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1997,7 +2063,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2008,7 +2074,7 @@
         <v>58</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2019,7 +2085,7 @@
         <v>58</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2030,7 +2096,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2041,7 +2107,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2052,7 +2118,7 @@
         <v>58</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2063,7 +2129,7 @@
         <v>58</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2074,7 +2140,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2082,10 +2148,10 @@
         <v>65</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2094,10 +2160,10 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46249.427471643517</v>
+        <v>46253.807392708331</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2108,7 +2174,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2119,7 +2185,7 @@
         <v>58</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2130,7 +2196,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2138,10 +2204,10 @@
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2149,22 +2215,22 @@
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific objects of Mechanical Driving Systems</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2175,7 +2241,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
@@ -2191,22 +2257,24 @@
     <col min="15" max="15" width="12.61328125" style="61" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34" style="61" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="33.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15" style="66" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.61328125" style="61" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="61"/>
+    <col min="18" max="18" width="30.61328125" style="61" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.921875" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.4609375" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20" style="61" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="61" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15" style="66" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="61" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.4609375" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="35.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="35.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="46" t="s">
         <v>42</v>
@@ -2239,7 +2307,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M1" s="37" t="s">
         <v>5</v>
@@ -2256,55 +2324,61 @@
       <c r="Q1" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="37" t="s">
-        <v>94</v>
+      <c r="R1" s="38" t="s">
+        <v>83</v>
       </c>
       <c r="S1" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="T1" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="U1" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="48" t="s">
+      <c r="V1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="W1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="62" t="s">
+      <c r="X1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="Y1" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z1" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="AA1" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB1" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC1" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z1" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA1" s="38" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G2" s="59" t="s">
         <v>9</v>
@@ -2338,65 +2412,70 @@
         <v>Motor.de.Combustão</v>
       </c>
       <c r="P2" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="Q2" s="30" t="s">
-        <v>124</v>
-      </c>
       <c r="R2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="30" t="str">
-        <f t="shared" ref="S2:S15" si="3">SUBSTITUTE(C2, "_", " ")</f>
+        <v>194</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="30" t="str">
+        <f t="shared" ref="T2:T15" si="3">SUBSTITUTE(C2, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="T2" s="30" t="str">
-        <f t="shared" ref="T2:T15" si="4">SUBSTITUTE(D2, "_", " ")</f>
+      <c r="U2" s="30" t="str">
+        <f t="shared" ref="U2:U15" si="4">SUBSTITUTE(D2, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U2" s="30" t="str">
-        <f t="shared" ref="U2:U15" si="5">SUBSTITUTE(E2, "_", " ")</f>
+      <c r="V2" s="30" t="str">
+        <f t="shared" ref="V2:V15" si="5">SUBSTITUTE(E2, "_", " ")</f>
         <v>Motorizados</v>
       </c>
-      <c r="V2" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="W2" s="60" t="str">
-        <f t="shared" ref="W2:W15" si="6">CONCATENATE("Key-MOT-",A2)</f>
+      <c r="W2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X2" s="60" t="str">
+        <f t="shared" ref="X2:X15" si="6">CONCATENATE("Key-MOT-",A2)</f>
         <v>Key-MOT-2</v>
       </c>
-      <c r="X2" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y2" s="29" t="s">
-        <v>101</v>
+      <c r="Y2" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA4" si="7">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Combustion engine</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA2" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB2" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F3" s="55" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G3" s="59" t="s">
         <v>9</v>
@@ -2414,82 +2493,87 @@
         <v>9</v>
       </c>
       <c r="L3" s="34" t="str">
-        <f t="shared" ref="L3" si="8">CONCATENATE("", C3)</f>
+        <f t="shared" ref="L3" si="7">CONCATENATE("", C3)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M3" s="34" t="str">
-        <f t="shared" ref="M3" si="9">CONCATENATE("", D3)</f>
+        <f t="shared" ref="M3" si="8">CONCATENATE("", D3)</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N3" s="34" t="str">
-        <f t="shared" ref="N3" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N3" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
         <v>Motorizados</v>
       </c>
       <c r="O3" s="30" t="str">
-        <f t="shared" ref="O3:O15" si="11">IF(ISNUMBER(FIND("Ifc",F3)),CONCATENATE("Classe IFC:   ",F3),F3)</f>
+        <f t="shared" ref="O3:O15" si="10">IF(ISNUMBER(FIND("Ifc",F3)),CONCATENATE("Classe IFC:   ",F3),F3)</f>
         <v>Motor.de.Acoplamento</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="30" t="str">
+        <v>195</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T3" s="30" t="str">
+      <c r="U3" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U3" s="30" t="str">
+      <c r="V3" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="V3" s="30" t="str">
-        <f t="shared" ref="V3:V15" si="12">SUBSTITUTE(C3, "_", " ")</f>
+      <c r="W3" s="30" t="str">
+        <f t="shared" ref="W3:W15" si="11">SUBSTITUTE(C3, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="W3" s="60" t="str">
+      <c r="X3" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-3</v>
       </c>
-      <c r="X3" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>102</v>
+      <c r="Y3" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z3" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA3" s="30" t="str">
-        <f t="shared" ref="AA3" si="13">_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Coupling motor</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB3" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G4" s="59" t="s">
         <v>9</v>
@@ -2519,70 +2603,75 @@
         <v>Motorizados</v>
       </c>
       <c r="O4" s="30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Motor.de.Acionamento.Correia</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="30" t="str">
+        <v>196</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T4" s="30" t="str">
+      <c r="U4" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U4" s="30" t="str">
+      <c r="V4" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="V4" s="30" t="str">
-        <f t="shared" si="12"/>
+      <c r="W4" s="30" t="str">
+        <f t="shared" si="11"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="W4" s="60" t="str">
+      <c r="X4" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-4</v>
       </c>
-      <c r="X4" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y4" s="29" t="s">
-        <v>103</v>
+      <c r="Y4" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z4" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA4" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Belt drive motor</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA4" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB4" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F5" s="55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G5" s="59" t="s">
         <v>9</v>
@@ -2600,82 +2689,87 @@
         <v>9</v>
       </c>
       <c r="L5" s="34" t="str">
-        <f t="shared" ref="L5" si="14">CONCATENATE("", C5)</f>
+        <f t="shared" ref="L5" si="12">CONCATENATE("", C5)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M5" s="34" t="str">
-        <f t="shared" ref="M5" si="15">CONCATENATE("", D5)</f>
+        <f t="shared" ref="M5" si="13">CONCATENATE("", D5)</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N5" s="34" t="str">
-        <f t="shared" ref="N5" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N5" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
         <v>Motorizados</v>
       </c>
       <c r="O5" s="30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Motor.de.Acionamento.Direto</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="30" t="str">
+        <v>197</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T5" s="30" t="str">
+      <c r="U5" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U5" s="30" t="str">
+      <c r="V5" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="V5" s="30" t="str">
-        <f t="shared" si="12"/>
+      <c r="W5" s="30" t="str">
+        <f t="shared" si="11"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="W5" s="60" t="str">
+      <c r="X5" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-5</v>
       </c>
-      <c r="X5" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y5" s="29" t="s">
-        <v>104</v>
+      <c r="Y5" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA5" s="30" t="str">
-        <f t="shared" ref="AA5" si="17">_xlfn.TRANSLATE(P5,"pt","en")</f>
-        <v>Direct drive motor</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA5" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G6" s="59" t="s">
         <v>9</v>
@@ -2693,11 +2787,11 @@
         <v>9</v>
       </c>
       <c r="L6" s="34" t="str">
-        <f t="shared" ref="L6:M13" si="18">CONCATENATE("", C6)</f>
+        <f t="shared" ref="L6:M13" si="15">CONCATENATE("", C6)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M6" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N6" s="34" t="str">
@@ -2705,70 +2799,75 @@
         <v>Maquinizados</v>
       </c>
       <c r="O6" s="30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Máquina.Motriz</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="30" t="str">
+        <v>198</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T6" s="30" t="str">
+      <c r="U6" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U6" s="30" t="str">
+      <c r="V6" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Maquinizados</v>
       </c>
-      <c r="V6" s="30" t="str">
-        <f t="shared" si="12"/>
+      <c r="W6" s="30" t="str">
+        <f t="shared" si="11"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="W6" s="60" t="str">
+      <c r="X6" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-6</v>
       </c>
-      <c r="X6" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y6" s="29" t="s">
-        <v>110</v>
+      <c r="Y6" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z6" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA6" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P6,"pt","en")</f>
-        <v>Engine that converts fuel into mechanical energy through combustion</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA6" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB6" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G7" s="59" t="s">
         <v>9</v>
@@ -2786,11 +2885,11 @@
         <v>9</v>
       </c>
       <c r="L7" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M7" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N7" s="34" t="str">
@@ -2798,70 +2897,75 @@
         <v>Maquinizados</v>
       </c>
       <c r="O7" s="30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Máquina.de.Combustão.Externa</v>
       </c>
       <c r="P7" s="30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q7" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="30" t="str">
+        <v>199</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T7" s="30" t="str">
+      <c r="U7" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U7" s="30" t="str">
+      <c r="V7" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Maquinizados</v>
       </c>
-      <c r="V7" s="30" t="str">
-        <f t="shared" si="12"/>
+      <c r="W7" s="30" t="str">
+        <f t="shared" si="11"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="W7" s="60" t="str">
+      <c r="X7" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-7</v>
       </c>
-      <c r="X7" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y7" s="29" t="s">
-        <v>112</v>
+      <c r="Y7" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA7" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Engine that converts fuel into mechanical energy through external combustion</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA7" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB7" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC7" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G8" s="59" t="s">
         <v>9</v>
@@ -2879,11 +2983,11 @@
         <v>9</v>
       </c>
       <c r="L8" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M8" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N8" s="34" t="str">
@@ -2891,70 +2995,75 @@
         <v>Maquinizados</v>
       </c>
       <c r="O8" s="30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Máquina.de.Combustão.Interna</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="30" t="str">
+        <v>200</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T8" s="30" t="str">
+      <c r="U8" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U8" s="30" t="str">
+      <c r="V8" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Maquinizados</v>
       </c>
-      <c r="V8" s="30" t="str">
-        <f t="shared" si="12"/>
+      <c r="W8" s="30" t="str">
+        <f t="shared" si="11"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="W8" s="60" t="str">
+      <c r="X8" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-8</v>
       </c>
-      <c r="X8" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y8" s="29" t="s">
-        <v>111</v>
+      <c r="Y8" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA8" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
-        <v>Engine that converts fuel into mechanical energy through internal combustion</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA8" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB8" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC8" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="58">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G9" s="59" t="s">
         <v>9</v>
@@ -2972,15 +3081,15 @@
         <v>9</v>
       </c>
       <c r="L9" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M9" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N9" s="34" t="str">
-        <f t="shared" ref="N9:N11" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N9:N11" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
         <v>Elevadores</v>
       </c>
       <c r="O9" s="30" t="str">
@@ -2988,66 +3097,71 @@
         <v>Elevador.Hidráulico</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="30" t="str">
-        <f t="shared" ref="S9:S14" si="20">SUBSTITUTE(C9, "_", " ")</f>
+        <v>201</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="30" t="str">
+        <f t="shared" ref="T9:T14" si="17">SUBSTITUTE(C9, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="T9" s="30" t="str">
-        <f t="shared" ref="T9:T14" si="21">SUBSTITUTE(D9, "_", " ")</f>
+      <c r="U9" s="30" t="str">
+        <f t="shared" ref="U9:U14" si="18">SUBSTITUTE(D9, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U9" s="30" t="str">
-        <f t="shared" ref="U9:U14" si="22">SUBSTITUTE(E9, "_", " ")</f>
+      <c r="V9" s="30" t="str">
+        <f t="shared" ref="V9:V14" si="19">SUBSTITUTE(E9, "_", " ")</f>
         <v>Elevadores</v>
       </c>
-      <c r="V9" s="30" t="str">
-        <f t="shared" ref="V9:V14" si="23">SUBSTITUTE(C9, "_", " ")</f>
+      <c r="W9" s="30" t="str">
+        <f t="shared" ref="W9:W14" si="20">SUBSTITUTE(C9, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="W9" s="60" t="str">
+      <c r="X9" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-9</v>
       </c>
-      <c r="X9" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y9" s="29" t="s">
-        <v>165</v>
+      <c r="Y9" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA9" s="30" t="str">
-        <f t="shared" ref="AA9:AA11" si="24">_xlfn.TRANSLATE(P9,"pt","en")</f>
-        <v>Elevator to a few floors without carrying heavy loads</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA9" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB9" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC9" s="30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="58">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G10" s="59" t="s">
         <v>9</v>
@@ -3065,82 +3179,87 @@
         <v>9</v>
       </c>
       <c r="L10" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M10" s="34" t="str">
+        <f t="shared" si="15"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="N10" s="34" t="str">
+        <f t="shared" si="16"/>
+        <v>Elevadores</v>
+      </c>
+      <c r="O10" s="30" t="str">
+        <f t="shared" ref="O10:O14" si="21">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),F10)</f>
+        <v>Elevador.MR</v>
+      </c>
+      <c r="P10" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q10" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="S10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="30" t="str">
+        <f t="shared" si="17"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U10" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="N10" s="34" t="str">
+      <c r="V10" s="30" t="str">
         <f t="shared" si="19"/>
         <v>Elevadores</v>
       </c>
-      <c r="O10" s="30" t="str">
-        <f t="shared" ref="O10:O14" si="25">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),F10)</f>
-        <v>Elevador.MR</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q10" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="R10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="30" t="str">
+      <c r="W10" s="30" t="str">
         <f t="shared" si="20"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T10" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="U10" s="30" t="str">
-        <f t="shared" si="22"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="V10" s="30" t="str">
-        <f t="shared" si="23"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="W10" s="60" t="str">
+      <c r="X10" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-10</v>
       </c>
-      <c r="X10" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y10" s="29" t="s">
-        <v>165</v>
+      <c r="Y10" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA10" s="30" t="str">
-        <f t="shared" si="24"/>
-        <v>Traction Elevator with Machine Room</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB10" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC10" s="30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="58">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G11" s="59" t="s">
         <v>9</v>
@@ -3158,82 +3277,87 @@
         <v>9</v>
       </c>
       <c r="L11" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M11" s="34" t="str">
+        <f t="shared" si="15"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="N11" s="34" t="str">
+        <f t="shared" si="16"/>
+        <v>Elevadores</v>
+      </c>
+      <c r="O11" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elevador.MRL</v>
+      </c>
+      <c r="P11" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q11" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="R11" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="30" t="str">
+        <f t="shared" si="17"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U11" s="30" t="str">
         <f t="shared" si="18"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="N11" s="34" t="str">
+      <c r="V11" s="30" t="str">
         <f t="shared" si="19"/>
         <v>Elevadores</v>
       </c>
-      <c r="O11" s="30" t="str">
-        <f t="shared" si="25"/>
-        <v>Elevador.MRL</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q11" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="R11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="30" t="str">
+      <c r="W11" s="30" t="str">
         <f t="shared" si="20"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T11" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="U11" s="30" t="str">
-        <f t="shared" si="22"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="V11" s="30" t="str">
-        <f t="shared" si="23"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="W11" s="60" t="str">
+      <c r="X11" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-11</v>
       </c>
-      <c r="X11" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y11" s="29" t="s">
-        <v>165</v>
+      <c r="Y11" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA11" s="30" t="str">
-        <f t="shared" si="24"/>
-        <v>Elevator with hoisting pulley without machine room</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA11" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB11" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC11" s="30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="58">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G12" s="59" t="s">
         <v>9</v>
@@ -3251,11 +3375,11 @@
         <v>9</v>
       </c>
       <c r="L12" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M12" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N12" s="34" t="str">
@@ -3263,70 +3387,75 @@
         <v>Elevadores</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" ref="O12:O13" si="26">IF(ISNUMBER(FIND("Ifc",F12)),CONCATENATE("Classe IFC:   ",F12),F12)</f>
+        <f t="shared" ref="O12:O13" si="22">IF(ISNUMBER(FIND("Ifc",F12)),CONCATENATE("Classe IFC:   ",F12),F12)</f>
         <v>Plataforma</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="30" t="str">
-        <f t="shared" ref="S12:S13" si="27">SUBSTITUTE(C12, "_", " ")</f>
+        <v>204</v>
+      </c>
+      <c r="S12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="30" t="str">
+        <f t="shared" ref="T12:T13" si="23">SUBSTITUTE(C12, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="T12" s="30" t="str">
-        <f t="shared" ref="T12:T13" si="28">SUBSTITUTE(D12, "_", " ")</f>
+      <c r="U12" s="30" t="str">
+        <f t="shared" ref="U12:U13" si="24">SUBSTITUTE(D12, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U12" s="30" t="str">
-        <f t="shared" ref="U12:U13" si="29">SUBSTITUTE(E12, "_", " ")</f>
+      <c r="V12" s="30" t="str">
+        <f t="shared" ref="V12:V13" si="25">SUBSTITUTE(E12, "_", " ")</f>
         <v>Elevadores</v>
       </c>
-      <c r="V12" s="30" t="str">
-        <f t="shared" ref="V12:V13" si="30">SUBSTITUTE(C12, "_", " ")</f>
+      <c r="W12" s="30" t="str">
+        <f t="shared" ref="W12:W13" si="26">SUBSTITUTE(C12, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="W12" s="60" t="str">
+      <c r="X12" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-12</v>
       </c>
-      <c r="X12" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y12" s="29" t="s">
+      <c r="Y12" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z12" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA12" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB12" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC12" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z12" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA12" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P12,"pt","en")</f>
-        <v>Lifting Platform</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="58">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G13" s="59" t="s">
         <v>9</v>
@@ -3344,11 +3473,11 @@
         <v>9</v>
       </c>
       <c r="L13" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M13" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N13" s="34" t="str">
@@ -3356,70 +3485,75 @@
         <v>Elevadores</v>
       </c>
       <c r="O13" s="30" t="str">
+        <f t="shared" si="22"/>
+        <v>Plataforma.Articulada</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q13" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="R13" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="S13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="30" t="str">
+        <f t="shared" si="23"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U13" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V13" s="30" t="str">
+        <f t="shared" si="25"/>
+        <v>Elevadores</v>
+      </c>
+      <c r="W13" s="30" t="str">
         <f t="shared" si="26"/>
-        <v>Plataforma.Articulada</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="R13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="30" t="str">
-        <f t="shared" si="27"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T13" s="30" t="str">
-        <f t="shared" si="28"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="U13" s="30" t="str">
-        <f t="shared" si="29"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="V13" s="30" t="str">
-        <f t="shared" si="30"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="W13" s="60" t="str">
+      <c r="X13" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-13</v>
       </c>
-      <c r="X13" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y13" s="29" t="s">
+      <c r="Y13" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z13" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA13" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB13" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC13" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z13" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA13" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P13,"pt","en")</f>
-        <v>Articulated lifting platform</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="58">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G14" s="59" t="s">
         <v>9</v>
@@ -3437,11 +3571,11 @@
         <v>9</v>
       </c>
       <c r="L14" s="34" t="str">
-        <f t="shared" ref="L14" si="31">CONCATENATE("", C14)</f>
+        <f t="shared" ref="L14" si="27">CONCATENATE("", C14)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M14" s="34" t="str">
-        <f t="shared" ref="M14" si="32">CONCATENATE("", D14)</f>
+        <f t="shared" ref="M14" si="28">CONCATENATE("", D14)</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N14" s="34" t="str">
@@ -3449,71 +3583,76 @@
         <v>Elevadores</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>Plataforma.Cesto</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R14" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="30" t="str">
+        <v>206</v>
+      </c>
+      <c r="S14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="30" t="str">
+        <f t="shared" si="17"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U14" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V14" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Elevadores</v>
+      </c>
+      <c r="W14" s="30" t="str">
         <f t="shared" si="20"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T14" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="U14" s="30" t="str">
-        <f t="shared" si="22"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="V14" s="30" t="str">
-        <f t="shared" si="23"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="W14" s="60" t="str">
+      <c r="X14" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-14</v>
       </c>
-      <c r="X14" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="29" t="s">
+      <c r="Y14" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z14" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA14" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB14" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC14" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z14" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA14" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P14,"pt","en")</f>
-        <v>Basket lifting platform</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="58">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" s="63" t="s">
         <v>192</v>
       </c>
-      <c r="E15" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>194</v>
-      </c>
       <c r="G15" s="64" t="s">
         <v>9</v>
       </c>
@@ -3530,83 +3669,88 @@
         <v>9</v>
       </c>
       <c r="L15" s="34" t="str">
-        <f t="shared" ref="L15:M15" si="33">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:M15" si="29">CONCATENATE("", C15)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M15" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="29"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N15" s="34" t="str">
-        <f t="shared" ref="N15" si="34">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N15" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
         <v>Acessórios Motrizes</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>Acessório.Motriz</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="30" t="str">
+        <v>207</v>
+      </c>
+      <c r="S15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="30" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="T15" s="30" t="str">
+      <c r="U15" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="U15" s="30" t="str">
+      <c r="V15" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Acessórios.Motrizes</v>
       </c>
-      <c r="V15" s="30" t="str">
-        <f t="shared" si="12"/>
+      <c r="W15" s="30" t="str">
+        <f t="shared" si="11"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="W15" s="60" t="str">
+      <c r="X15" s="60" t="str">
         <f t="shared" si="6"/>
         <v>Key-MOT-15</v>
       </c>
-      <c r="X15" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y15" s="29" t="s">
-        <v>100</v>
+      <c r="Y15" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA15" s="30" t="str">
-        <f t="shared" ref="AA15" si="35">_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Mechanical Accessory</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA15" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB15" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC15" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="58">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="F16" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>180</v>
-      </c>
       <c r="G16" s="64" t="s">
         <v>9</v>
       </c>
@@ -3623,83 +3767,88 @@
         <v>9</v>
       </c>
       <c r="L16" s="34" t="str">
-        <f t="shared" ref="L16" si="36">CONCATENATE("", C16)</f>
+        <f t="shared" ref="L16" si="31">CONCATENATE("", C16)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M16" s="34" t="str">
-        <f t="shared" ref="M16" si="37">CONCATENATE("", D16)</f>
+        <f t="shared" ref="M16" si="32">CONCATENATE("", D16)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N16" s="34" t="str">
-        <f t="shared" ref="N16" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N16" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16" si="39">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
+        <f t="shared" ref="O16" si="34">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
         <v>Máquina</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="30" t="str">
-        <f t="shared" ref="S16" si="40">SUBSTITUTE(C16, "_", " ")</f>
+        <v>208</v>
+      </c>
+      <c r="S16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="30" t="str">
+        <f t="shared" ref="T16" si="35">SUBSTITUTE(C16, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="T16" s="30" t="str">
-        <f t="shared" ref="T16" si="41">SUBSTITUTE(D16, "_", " ")</f>
+      <c r="U16" s="30" t="str">
+        <f t="shared" ref="U16" si="36">SUBSTITUTE(D16, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
-      <c r="U16" s="30" t="str">
-        <f t="shared" ref="U16" si="42">SUBSTITUTE(E16, "_", " ")</f>
+      <c r="V16" s="30" t="str">
+        <f t="shared" ref="V16" si="37">SUBSTITUTE(E16, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="V16" s="30" t="str">
-        <f t="shared" ref="V16" si="43">SUBSTITUTE(C16, "_", " ")</f>
+      <c r="W16" s="30" t="str">
+        <f t="shared" ref="W16" si="38">SUBSTITUTE(C16, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="W16" s="60" t="str">
-        <f t="shared" ref="W16" si="44">CONCATENATE("Key-MOT-",A16)</f>
+      <c r="X16" s="60" t="str">
+        <f t="shared" ref="X16" si="39">CONCATENATE("Key-MOT-",A16)</f>
         <v>Key-MOT-16</v>
       </c>
-      <c r="X16" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y16" s="29" t="s">
-        <v>100</v>
+      <c r="Y16" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA16" s="30" t="str">
-        <f t="shared" ref="AA16" si="45">_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>Machine</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA16" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB16" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC16" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="58">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="E17" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" s="63" t="s">
-        <v>181</v>
-      </c>
       <c r="G17" s="64" t="s">
         <v>9</v>
       </c>
@@ -3716,82 +3865,87 @@
         <v>9</v>
       </c>
       <c r="L17" s="34" t="str">
-        <f t="shared" ref="L17:L18" si="46">CONCATENATE("", C17)</f>
+        <f t="shared" ref="L17:L18" si="40">CONCATENATE("", C17)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M17" s="34" t="str">
-        <f t="shared" ref="M17:M18" si="47">CONCATENATE("", D17)</f>
+        <f t="shared" ref="M17:M18" si="41">CONCATENATE("", D17)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N17" s="34" t="str">
-        <f t="shared" ref="N17:N18" si="48">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N17:N18" si="42">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" ref="O17:O18" si="49">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
+        <f t="shared" ref="O17:O18" si="43">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
         <v>Bomba</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="30" t="str">
-        <f t="shared" ref="S17:S18" si="50">SUBSTITUTE(C17, "_", " ")</f>
+        <v>209</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="30" t="str">
+        <f t="shared" ref="T17:T18" si="44">SUBSTITUTE(C17, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="T17" s="30" t="str">
-        <f t="shared" ref="T17:T18" si="51">SUBSTITUTE(D17, "_", " ")</f>
+      <c r="U17" s="30" t="str">
+        <f t="shared" ref="U17:U18" si="45">SUBSTITUTE(D17, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
-      <c r="U17" s="30" t="str">
-        <f t="shared" ref="U17:U18" si="52">SUBSTITUTE(E17, "_", " ")</f>
+      <c r="V17" s="30" t="str">
+        <f t="shared" ref="V17:V18" si="46">SUBSTITUTE(E17, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="V17" s="30" t="str">
-        <f t="shared" ref="V17:V18" si="53">SUBSTITUTE(C17, "_", " ")</f>
+      <c r="W17" s="30" t="str">
+        <f t="shared" ref="W17:W18" si="47">SUBSTITUTE(C17, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="W17" s="60" t="str">
-        <f t="shared" ref="W17:W18" si="54">CONCATENATE("Key-MOT-",A17)</f>
+      <c r="X17" s="60" t="str">
+        <f t="shared" ref="X17:X18" si="48">CONCATENATE("Key-MOT-",A17)</f>
         <v>Key-MOT-17</v>
       </c>
-      <c r="X17" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y17" s="29" t="s">
-        <v>100</v>
+      <c r="Y17" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA17" s="30" t="str">
-        <f t="shared" ref="AA17:AA18" si="55">_xlfn.TRANSLATE(P17,"pt","en")</f>
-        <v>Pump</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA17" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB17" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC17" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="58">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F18" s="63" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G18" s="64" t="s">
         <v>9</v>
@@ -3809,82 +3963,87 @@
         <v>9</v>
       </c>
       <c r="L18" s="34" t="str">
+        <f t="shared" si="40"/>
+        <v>De.Força.Motriz</v>
+      </c>
+      <c r="M18" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v>Maquinárias</v>
+      </c>
+      <c r="N18" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>Máquinas</v>
+      </c>
+      <c r="O18" s="30" t="str">
+        <f t="shared" si="43"/>
+        <v>Motor</v>
+      </c>
+      <c r="P18" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q18" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="30" t="str">
+        <f t="shared" si="44"/>
+        <v>De.Força.Motriz</v>
+      </c>
+      <c r="U18" s="30" t="str">
+        <f t="shared" si="45"/>
+        <v>Maquinárias</v>
+      </c>
+      <c r="V18" s="30" t="str">
         <f t="shared" si="46"/>
+        <v>Máquinas</v>
+      </c>
+      <c r="W18" s="30" t="str">
+        <f t="shared" si="47"/>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="M18" s="34" t="str">
-        <f t="shared" si="47"/>
-        <v>Maquinárias</v>
-      </c>
-      <c r="N18" s="34" t="str">
+      <c r="X18" s="60" t="str">
         <f t="shared" si="48"/>
-        <v>Máquinas</v>
-      </c>
-      <c r="O18" s="30" t="str">
-        <f t="shared" si="49"/>
-        <v>Motor</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q18" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="R18" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="30" t="str">
-        <f t="shared" si="50"/>
-        <v>De.Força.Motriz</v>
-      </c>
-      <c r="T18" s="30" t="str">
-        <f t="shared" si="51"/>
-        <v>Maquinárias</v>
-      </c>
-      <c r="U18" s="30" t="str">
-        <f t="shared" si="52"/>
-        <v>Máquinas</v>
-      </c>
-      <c r="V18" s="30" t="str">
-        <f t="shared" si="53"/>
-        <v>De.Força.Motriz</v>
-      </c>
-      <c r="W18" s="60" t="str">
-        <f t="shared" si="54"/>
         <v>Key-MOT-18</v>
       </c>
-      <c r="X18" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y18" s="29" t="s">
-        <v>100</v>
+      <c r="Y18" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA18" s="30" t="str">
-        <f t="shared" si="55"/>
-        <v>Engine</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA18" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB18" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC18" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="58">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F19" s="63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G19" s="64" t="s">
         <v>9</v>
@@ -3902,209 +4061,219 @@
         <v>9</v>
       </c>
       <c r="L19" s="34" t="str">
-        <f t="shared" ref="L19" si="56">CONCATENATE("", C19)</f>
+        <f t="shared" ref="L19" si="49">CONCATENATE("", C19)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M19" s="34" t="str">
-        <f t="shared" ref="M19" si="57">CONCATENATE("", D19)</f>
+        <f t="shared" ref="M19" si="50">CONCATENATE("", D19)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N19" s="34" t="str">
-        <f t="shared" ref="N19" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N19" si="51">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" ref="O19" si="59">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
+        <f t="shared" ref="O19" si="52">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
         <v>Elevador</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="30" t="str">
-        <f t="shared" ref="S19" si="60">SUBSTITUTE(C19, "_", " ")</f>
+        <v>211</v>
+      </c>
+      <c r="S19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="30" t="str">
+        <f t="shared" ref="T19" si="53">SUBSTITUTE(C19, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="T19" s="30" t="str">
-        <f t="shared" ref="T19" si="61">SUBSTITUTE(D19, "_", " ")</f>
+      <c r="U19" s="30" t="str">
+        <f t="shared" ref="U19" si="54">SUBSTITUTE(D19, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
-      <c r="U19" s="30" t="str">
-        <f t="shared" ref="U19" si="62">SUBSTITUTE(E19, "_", " ")</f>
+      <c r="V19" s="30" t="str">
+        <f t="shared" ref="V19" si="55">SUBSTITUTE(E19, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="V19" s="30" t="str">
-        <f t="shared" ref="V19" si="63">SUBSTITUTE(C19, "_", " ")</f>
+      <c r="W19" s="30" t="str">
+        <f t="shared" ref="W19" si="56">SUBSTITUTE(C19, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="W19" s="60" t="str">
-        <f t="shared" ref="W19" si="64">CONCATENATE("Key-MOT-",A19)</f>
+      <c r="X19" s="60" t="str">
+        <f t="shared" ref="X19" si="57">CONCATENATE("Key-MOT-",A19)</f>
         <v>Key-MOT-19</v>
       </c>
-      <c r="X19" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y19" s="29" t="s">
-        <v>100</v>
+      <c r="Y19" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA19" s="30" t="str">
-        <f t="shared" ref="AA19" si="65">_xlfn.TRANSLATE(P19,"pt","en")</f>
-        <v>Elevator</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>215</v>
+      </c>
+      <c r="AA19" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB19" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC19" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="58">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F20" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="34" t="str">
+        <f t="shared" ref="L20" si="58">CONCATENATE("", C20)</f>
+        <v>De.Força.Motriz</v>
+      </c>
+      <c r="M20" s="34" t="str">
+        <f t="shared" ref="M20" si="59">CONCATENATE("", D20)</f>
+        <v>Maquinárias</v>
+      </c>
+      <c r="N20" s="34" t="str">
+        <f t="shared" ref="N20" si="60">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
+        <v>Máquinas</v>
+      </c>
+      <c r="O20" s="30" t="str">
+        <f t="shared" ref="O20" si="61">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
+        <v>Escada.Rolante</v>
+      </c>
+      <c r="P20" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q20" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="G20" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L20" s="34" t="str">
-        <f t="shared" ref="L20" si="66">CONCATENATE("", C20)</f>
+      <c r="R20" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="S20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T20" s="30" t="str">
+        <f t="shared" ref="T20" si="62">SUBSTITUTE(C20, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="M20" s="34" t="str">
-        <f t="shared" ref="M20" si="67">CONCATENATE("", D20)</f>
+      <c r="U20" s="30" t="str">
+        <f t="shared" ref="U20" si="63">SUBSTITUTE(D20, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
-      <c r="N20" s="34" t="str">
-        <f t="shared" ref="N20" si="68">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
+      <c r="V20" s="30" t="str">
+        <f t="shared" ref="V20" si="64">SUBSTITUTE(E20, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="O20" s="30" t="str">
-        <f t="shared" ref="O20" si="69">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
-        <v>Escada.Rolante</v>
-      </c>
-      <c r="P20" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q20" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="R20" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="30" t="str">
-        <f t="shared" ref="S20" si="70">SUBSTITUTE(C20, "_", " ")</f>
+      <c r="W20" s="30" t="str">
+        <f t="shared" ref="W20" si="65">SUBSTITUTE(C20, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="T20" s="30" t="str">
-        <f t="shared" ref="T20" si="71">SUBSTITUTE(D20, "_", " ")</f>
-        <v>Maquinárias</v>
-      </c>
-      <c r="U20" s="30" t="str">
-        <f t="shared" ref="U20" si="72">SUBSTITUTE(E20, "_", " ")</f>
-        <v>Máquinas</v>
-      </c>
-      <c r="V20" s="30" t="str">
-        <f t="shared" ref="V20" si="73">SUBSTITUTE(C20, "_", " ")</f>
-        <v>De.Força.Motriz</v>
-      </c>
-      <c r="W20" s="60" t="str">
-        <f t="shared" ref="W20" si="74">CONCATENATE("Key-MOT-",A20)</f>
+      <c r="X20" s="60" t="str">
+        <f t="shared" ref="X20" si="66">CONCATENATE("Key-MOT-",A20)</f>
         <v>Key-MOT-20</v>
       </c>
-      <c r="X20" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y20" s="29" t="s">
-        <v>100</v>
+      <c r="Y20" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA20" s="30" t="str">
-        <f t="shared" ref="AA20" si="75">_xlfn.TRANSLATE(P20,"pt","en")</f>
-        <v>Escalator</v>
+        <v>215</v>
+      </c>
+      <c r="AA20" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB20" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC20" s="30" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA740">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC740">
     <sortCondition ref="F2:F740"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B20">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 R1:X1 Z1">
-    <cfRule type="cellIs" dxfId="25" priority="230" operator="equal">
+  <conditionalFormatting sqref="A1:O1 S1:Y1 AC1">
+    <cfRule type="cellIs" dxfId="25" priority="231" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="2009"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2010"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1666"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1667"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="duplicateValues" dxfId="22" priority="2064"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F8">
-    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F14">
-    <cfRule type="duplicateValues" dxfId="15" priority="2101"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F20">
-    <cfRule type="duplicateValues" dxfId="14" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="2019"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="2025"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2026"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2027"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2069"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2026"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2027"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2028"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2070"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X20">
-    <cfRule type="containsText" dxfId="8" priority="57" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",X2)))</formula>
+  <conditionalFormatting sqref="Y2:Y20">
+    <cfRule type="containsText" dxfId="8" priority="58" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA14">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+  <conditionalFormatting sqref="R2:R14">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4449,10 +4618,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>9</v>
@@ -4464,7 +4633,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H2" s="51" t="s">
         <v>9</v>
@@ -4508,58 +4677,58 @@
         <v>3</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H3" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P3" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q3" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I3" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J3" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O3" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P3" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q3" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R3" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S3" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4567,58 +4736,58 @@
         <v>4</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H4" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P4" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q4" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J4" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L4" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P4" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R4" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S4" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4626,58 +4795,58 @@
         <v>5</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H5" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J5" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P5" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q5" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P5" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R5" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S5" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4685,58 +4854,58 @@
         <v>6</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H6" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J6" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L6" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P6" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I6" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J6" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R6" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S6" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4744,58 +4913,58 @@
         <v>7</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H7" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J7" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J7" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L7" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P7" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q7" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R7" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S7" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4803,58 +4972,58 @@
         <v>8</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H8" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P8" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J8" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P8" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R8" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S8" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4862,58 +5031,58 @@
         <v>9</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H9" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L9" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J9" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L9" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q9" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R9" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S9" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4921,58 +5090,58 @@
         <v>10</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H10" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="J10" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="L10" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O10" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="R10" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S10" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/SIS/Ontologia_Motriz.xlsx
+++ b/Versão5/SIS/Ontologia_Motriz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BA4B6C-E283-40CB-9145-1AE01342D846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B89646-EC47-426F-9FEC-EAB9A0FE2E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="222">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -719,13 +719,25 @@
     <t>Atributo IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parâmetro Rvt</t>
   </si>
   <si>
     <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
   </si>
 </sst>
 </file>
@@ -816,7 +828,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -955,6 +967,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1068,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1263,12 +1281,130 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1508,14 +1644,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1958,14 +2086,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="47.15234375" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -1976,7 +2104,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -1987,7 +2115,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -1998,7 +2126,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2009,7 +2137,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2021,7 +2149,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2033,7 +2161,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2044,7 +2172,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="39" t="s">
         <v>54</v>
       </c>
@@ -2055,7 +2183,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2066,7 +2194,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2077,7 +2205,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2088,7 +2216,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2099,7 +2227,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2110,7 +2238,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2121,7 +2249,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2132,7 +2260,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2143,7 +2271,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2154,19 +2282,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46253.807392708331</v>
+        <v>46260.360267013886</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2177,7 +2305,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2188,7 +2316,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2199,7 +2327,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2210,7 +2338,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2221,7 +2349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -2241,38 +2369,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC20"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC21"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.61328125" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.61328125" style="61" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="33.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.61328125" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20" style="61" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15" style="66" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46" style="61" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="44.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.85546875" style="61" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" style="66" customWidth="1"/>
     <col min="28" max="28" width="6" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="61"/>
+    <col min="29" max="29" width="10.42578125" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="35.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="35.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>90</v>
       </c>
@@ -2346,10 +2474,10 @@
         <v>8</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AA1" s="37" t="s">
         <v>213</v>
@@ -2361,7 +2489,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="58">
         <v>2</v>
       </c>
@@ -2445,20 +2573,20 @@
       <c r="Y2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>215</v>
+      <c r="Z2" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AB2" s="30" t="s">
-        <v>215</v>
+      <c r="AB2" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58">
         <v>3</v>
       </c>
@@ -2543,20 +2671,20 @@
       <c r="Y3" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z3" s="30" t="s">
-        <v>215</v>
+      <c r="Z3" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="AB3" s="30" t="s">
-        <v>215</v>
+      <c r="AB3" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="58">
         <v>4</v>
       </c>
@@ -2641,20 +2769,20 @@
       <c r="Y4" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z4" s="30" t="s">
-        <v>215</v>
+      <c r="Z4" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="AB4" s="30" t="s">
-        <v>215</v>
+      <c r="AB4" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58">
         <v>5</v>
       </c>
@@ -2739,20 +2867,20 @@
       <c r="Y5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z5" s="30" t="s">
-        <v>215</v>
+      <c r="Z5" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="AB5" s="30" t="s">
-        <v>215</v>
+      <c r="AB5" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="58">
         <v>6</v>
       </c>
@@ -2837,20 +2965,20 @@
       <c r="Y6" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z6" s="30" t="s">
-        <v>215</v>
+      <c r="Z6" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="AB6" s="30" t="s">
-        <v>215</v>
+      <c r="AB6" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58">
         <v>7</v>
       </c>
@@ -2935,20 +3063,20 @@
       <c r="Y7" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z7" s="30" t="s">
-        <v>215</v>
+      <c r="Z7" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="AB7" s="30" t="s">
-        <v>215</v>
+      <c r="AB7" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58">
         <v>8</v>
       </c>
@@ -3033,20 +3161,20 @@
       <c r="Y8" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z8" s="30" t="s">
-        <v>215</v>
+      <c r="Z8" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="AB8" s="30" t="s">
-        <v>215</v>
+      <c r="AB8" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58">
         <v>9</v>
       </c>
@@ -3131,20 +3259,20 @@
       <c r="Y9" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z9" s="30" t="s">
-        <v>215</v>
+      <c r="Z9" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB9" s="30" t="s">
-        <v>215</v>
+      <c r="AB9" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58">
         <v>10</v>
       </c>
@@ -3229,20 +3357,20 @@
       <c r="Y10" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z10" s="30" t="s">
-        <v>215</v>
+      <c r="Z10" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB10" s="30" t="s">
-        <v>215</v>
+      <c r="AB10" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>11</v>
       </c>
@@ -3327,20 +3455,20 @@
       <c r="Y11" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z11" s="30" t="s">
-        <v>215</v>
+      <c r="Z11" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB11" s="30" t="s">
-        <v>215</v>
+      <c r="AB11" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="58">
         <v>12</v>
       </c>
@@ -3425,20 +3553,20 @@
       <c r="Y12" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z12" s="30" t="s">
-        <v>215</v>
+      <c r="Z12" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB12" s="30" t="s">
-        <v>215</v>
+      <c r="AB12" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>13</v>
       </c>
@@ -3523,20 +3651,20 @@
       <c r="Y13" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z13" s="30" t="s">
-        <v>215</v>
+      <c r="Z13" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB13" s="30" t="s">
-        <v>215</v>
+      <c r="AB13" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
         <v>14</v>
       </c>
@@ -3621,20 +3749,20 @@
       <c r="Y14" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z14" s="30" t="s">
-        <v>215</v>
+      <c r="Z14" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB14" s="30" t="s">
-        <v>215</v>
+      <c r="AB14" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>15</v>
       </c>
@@ -3719,20 +3847,20 @@
       <c r="Y15" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z15" s="30" t="s">
-        <v>215</v>
+      <c r="Z15" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB15" s="30" t="s">
-        <v>215</v>
+      <c r="AB15" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="58">
         <v>16</v>
       </c>
@@ -3817,20 +3945,20 @@
       <c r="Y16" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z16" s="30" t="s">
-        <v>215</v>
+      <c r="Z16" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB16" s="30" t="s">
-        <v>215</v>
+      <c r="AB16" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58">
         <v>17</v>
       </c>
@@ -3915,20 +4043,20 @@
       <c r="Y17" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z17" s="30" t="s">
-        <v>215</v>
+      <c r="Z17" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB17" s="30" t="s">
-        <v>215</v>
+      <c r="AB17" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58">
         <v>18</v>
       </c>
@@ -4013,20 +4141,20 @@
       <c r="Y18" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z18" s="30" t="s">
-        <v>215</v>
+      <c r="Z18" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB18" s="30" t="s">
-        <v>215</v>
+      <c r="AB18" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>19</v>
       </c>
@@ -4111,20 +4239,20 @@
       <c r="Y19" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z19" s="30" t="s">
-        <v>215</v>
+      <c r="Z19" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB19" s="30" t="s">
-        <v>215</v>
+      <c r="AB19" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>20</v>
       </c>
@@ -4199,27 +4327,127 @@
         <v>Máquinas</v>
       </c>
       <c r="W20" s="30" t="str">
-        <f t="shared" ref="W20" si="65">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="W20:W21" si="65">SUBSTITUTE(C20, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="X20" s="60" t="str">
-        <f t="shared" ref="X20" si="66">CONCATENATE("Key-MOT-",A20)</f>
+        <f t="shared" ref="X20:X21" si="66">CONCATENATE("Key-MOT-",A20)</f>
         <v>Key-MOT-20</v>
       </c>
       <c r="Y20" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z20" s="30" t="s">
-        <v>215</v>
+      <c r="Z20" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB20" s="30" t="s">
-        <v>215</v>
+      <c r="AB20" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="58">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="G21" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L21" s="34" t="str">
+        <f t="shared" ref="L21:O21" si="67">SUBSTITUTE(CONCATENATE("", C21), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M21" s="34" t="str">
+        <f t="shared" si="67"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N21" s="34" t="str">
+        <f t="shared" si="67"/>
+        <v>Macros</v>
+      </c>
+      <c r="O21" s="34" t="str">
+        <f t="shared" si="67"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P21" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q21" s="67" t="str">
+        <f t="shared" ref="Q21" si="68">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R21" s="67" t="str">
+        <f t="shared" ref="R21" si="69">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T21" s="30" t="str">
+        <f t="shared" ref="T21:V21" si="70">SUBSTITUTE(C21, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U21" s="30" t="str">
+        <f t="shared" si="70"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V21" s="68" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="W21" s="30" t="str">
+        <f t="shared" si="65"/>
+        <v>De.API</v>
+      </c>
+      <c r="X21" s="60" t="str">
+        <f t="shared" si="66"/>
+        <v>Key-MOT-21</v>
+      </c>
+      <c r="Y21" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="69" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4227,55 +4455,75 @@
     <sortCondition ref="F2:F740"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B20">
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B20 A21">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 S1:Y1 AC1">
-    <cfRule type="cellIs" dxfId="25" priority="231" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="241" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="2010"/>
+  <conditionalFormatting sqref="F1 F15:F20 F22:F1048576">
+    <cfRule type="duplicateValues" dxfId="35" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1667"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="duplicateValues" dxfId="22" priority="2065"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="2075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F8">
-    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F14">
-    <cfRule type="duplicateValues" dxfId="15" priority="2102"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F20">
-    <cfRule type="duplicateValues" dxfId="14" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="2020"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="2026"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2027"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2028"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2070"/>
+  <conditionalFormatting sqref="F15:F20 F22:F1048576">
+    <cfRule type="duplicateValues" dxfId="24" priority="2030"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2036"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2038"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2080"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R14">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y20">
-    <cfRule type="containsText" dxfId="8" priority="58" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="18" priority="68" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <conditionalFormatting sqref="B21">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q21">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R21">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4288,15 +4536,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4361,7 +4609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4428,7 +4676,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4444,15 +4692,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -4475,7 +4723,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -4504,22 +4752,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4531,30 +4779,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.53515625" customWidth="1"/>
-    <col min="4" max="4" width="7.53515625" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.69140625" customWidth="1"/>
-    <col min="8" max="8" width="6.69140625" customWidth="1"/>
-    <col min="9" max="9" width="11.84375" customWidth="1"/>
-    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.53515625" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="2.84375" customWidth="1"/>
-    <col min="14" max="14" width="7.3046875" customWidth="1"/>
-    <col min="15" max="15" width="13.84375" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -4613,7 +4861,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4672,7 +4920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -4731,7 +4979,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -4790,7 +5038,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -4849,7 +5097,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -4908,7 +5156,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -4967,7 +5215,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -5026,7 +5274,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -5085,7 +5333,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>10</v>
       </c>

--- a/Versão5/SIS/Ontologia_Motriz.xlsx
+++ b/Versão5/SIS/Ontologia_Motriz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B89646-EC47-426F-9FEC-EAB9A0FE2E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8E2C39-9293-4BD9-845E-D947FA62576D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1298,113 +1298,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="36">
     <dxf>
       <font>
         <b val="0"/>
@@ -1476,6 +1370,46 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1644,6 +1578,64 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2086,14 +2078,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="47.140625" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="47.15234375" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2104,7 +2096,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2115,7 +2107,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2126,7 +2118,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2137,7 +2129,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2149,7 +2141,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2161,7 +2153,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2172,7 +2164,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="39" t="s">
         <v>54</v>
       </c>
@@ -2183,7 +2175,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2194,7 +2186,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2205,7 +2197,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2216,7 +2208,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2227,7 +2219,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2238,7 +2230,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2249,7 +2241,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2260,7 +2252,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2271,7 +2263,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2282,19 +2274,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46260.360267013886</v>
+        <v>46264.57058472222</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2305,7 +2297,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2316,7 +2308,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2327,7 +2319,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2338,7 +2330,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2349,7 +2341,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -2370,37 +2362,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3046875" style="61" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.53515625" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.3046875" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.69140625" style="61" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="46" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.85546875" style="61" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.28515625" style="66" customWidth="1"/>
+    <col min="17" max="17" width="44.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.3046875" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.84375" style="61" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.3046875" style="66" customWidth="1"/>
     <col min="28" max="28" width="6" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="61"/>
+    <col min="29" max="29" width="10.3828125" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="35.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="45" t="s">
         <v>90</v>
       </c>
@@ -2489,7 +2481,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>2</v>
       </c>
@@ -2586,7 +2578,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>3</v>
       </c>
@@ -2684,7 +2676,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>4</v>
       </c>
@@ -2782,7 +2774,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>5</v>
       </c>
@@ -2880,7 +2872,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>6</v>
       </c>
@@ -2978,7 +2970,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>7</v>
       </c>
@@ -3076,7 +3068,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>8</v>
       </c>
@@ -3174,7 +3166,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="58">
         <v>9</v>
       </c>
@@ -3272,7 +3264,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="58">
         <v>10</v>
       </c>
@@ -3370,7 +3362,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="58">
         <v>11</v>
       </c>
@@ -3468,7 +3460,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="58">
         <v>12</v>
       </c>
@@ -3566,7 +3558,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="58">
         <v>13</v>
       </c>
@@ -3664,7 +3656,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="58">
         <v>14</v>
       </c>
@@ -3762,7 +3754,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="58">
         <v>15</v>
       </c>
@@ -3860,7 +3852,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="58">
         <v>16</v>
       </c>
@@ -3958,7 +3950,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="58">
         <v>17</v>
       </c>
@@ -4056,7 +4048,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="58">
         <v>18</v>
       </c>
@@ -4154,7 +4146,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="58">
         <v>19</v>
       </c>
@@ -4252,7 +4244,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="58">
         <v>20</v>
       </c>
@@ -4350,7 +4342,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58">
         <v>21</v>
       </c>
@@ -4361,10 +4353,10 @@
         <v>217</v>
       </c>
       <c r="D21" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E21" s="63" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="63" t="s">
-        <v>219</v>
       </c>
       <c r="F21" s="63" t="s">
         <v>220</v>
@@ -4390,11 +4382,11 @@
       </c>
       <c r="M21" s="34" t="str">
         <f t="shared" si="67"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N21" s="34" t="str">
         <f t="shared" si="67"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O21" s="34" t="str">
         <f t="shared" si="67"/>
@@ -4420,11 +4412,11 @@
       </c>
       <c r="U21" s="30" t="str">
         <f t="shared" si="70"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V21" s="68" t="str">
         <f t="shared" si="70"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W21" s="30" t="str">
         <f t="shared" si="65"/>
@@ -4455,75 +4447,70 @@
     <sortCondition ref="F2:F740"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B20 A21">
-    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
+  <conditionalFormatting sqref="A2:B21">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 S1:Y1 AC1">
-    <cfRule type="cellIs" dxfId="36" priority="241" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="241" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F15:F20 F22:F1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="2020"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="2020"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="34" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="duplicateValues" dxfId="33" priority="2075"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2075"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F8">
-    <cfRule type="duplicateValues" dxfId="32" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F14">
-    <cfRule type="duplicateValues" dxfId="26" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F20 F22:F1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="2030"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2036"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2037"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2038"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F20">
-    <cfRule type="duplicateValues" dxfId="25" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F20 F22:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="2030"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2036"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="2037"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2038"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2080"/>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q21">
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R14">
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R21">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y20">
-    <cfRule type="containsText" dxfId="18" priority="68" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="68" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q21">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R21">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4536,15 +4523,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4609,7 +4596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4676,7 +4663,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4692,15 +4679,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -4723,7 +4710,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -4752,22 +4739,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4779,30 +4766,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.53515625" customWidth="1"/>
+    <col min="4" max="4" width="7.53515625" customWidth="1"/>
+    <col min="5" max="5" width="7.69140625" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="27.69140625" customWidth="1"/>
+    <col min="8" max="8" width="6.69140625" customWidth="1"/>
+    <col min="9" max="9" width="11.84375" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53515625" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="2.85546875" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.84375" customWidth="1"/>
+    <col min="14" max="14" width="7.3046875" customWidth="1"/>
+    <col min="15" max="15" width="13.84375" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.3046875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -4861,7 +4848,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4920,7 +4907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -4979,7 +4966,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -5038,7 +5025,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -5097,7 +5084,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -5156,7 +5143,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -5215,7 +5202,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -5274,7 +5261,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -5333,7 +5320,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>

--- a/Versão5/SIS/Ontologia_Motriz.xlsx
+++ b/Versão5/SIS/Ontologia_Motriz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8E2C39-9293-4BD9-845E-D947FA62576D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1C14B-CF9D-49F3-998D-ED61717EA1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="242">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -734,10 +734,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1281,9 +1341,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1298,7 +1355,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="29">
     <dxf>
       <font>
         <b val="0"/>
@@ -1373,81 +1430,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2078,14 +2065,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="47.15234375" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2096,7 +2083,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2107,7 +2094,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2118,7 +2105,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2129,7 +2116,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2141,7 +2128,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2153,7 +2140,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2164,7 +2151,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="39" t="s">
         <v>54</v>
       </c>
@@ -2175,7 +2162,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2186,7 +2173,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2197,7 +2184,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2208,7 +2195,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2219,7 +2206,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2230,7 +2217,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2241,7 +2228,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2252,7 +2239,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2263,7 +2250,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2274,19 +2261,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46264.57058472222</v>
+        <v>46268.7008255787</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2297,7 +2284,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2308,7 +2295,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2319,7 +2306,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2330,7 +2317,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2341,7 +2328,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -2361,38 +2348,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC21"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.53515625" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.3046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.69140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="61" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="46" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.3046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.84375" style="61" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.3046875" style="66" customWidth="1"/>
+    <col min="17" max="17" width="44.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.85546875" style="61" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" style="66" customWidth="1"/>
     <col min="28" max="28" width="6" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.3828125" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="61"/>
+    <col min="29" max="29" width="10.42578125" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="35.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>90</v>
       </c>
@@ -2480,8 +2467,11 @@
       <c r="AC1" s="37" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD1" s="37" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="58">
         <v>2</v>
       </c>
@@ -2565,20 +2555,23 @@
       <c r="Y2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z2" s="69" t="s">
+      <c r="Z2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AB2" s="69" t="s">
+      <c r="AB2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD2" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58">
         <v>3</v>
       </c>
@@ -2652,9 +2645,8 @@
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="W3" s="30" t="str">
-        <f t="shared" ref="W3:W15" si="11">SUBSTITUTE(C3, "_", " ")</f>
-        <v>De.Motricidade</v>
+      <c r="W3" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X3" s="60" t="str">
         <f t="shared" si="6"/>
@@ -2663,20 +2655,23 @@
       <c r="Y3" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z3" s="69" t="s">
+      <c r="Z3" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="AB3" s="69" t="s">
+      <c r="AB3" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="58">
         <v>4</v>
       </c>
@@ -2750,9 +2745,8 @@
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="W4" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>De.Motricidade</v>
+      <c r="W4" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X4" s="60" t="str">
         <f t="shared" si="6"/>
@@ -2761,20 +2755,23 @@
       <c r="Y4" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z4" s="69" t="s">
+      <c r="Z4" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="AB4" s="69" t="s">
+      <c r="AB4" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD4" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58">
         <v>5</v>
       </c>
@@ -2809,15 +2806,15 @@
         <v>9</v>
       </c>
       <c r="L5" s="34" t="str">
-        <f t="shared" ref="L5" si="12">CONCATENATE("", C5)</f>
+        <f t="shared" ref="L5" si="11">CONCATENATE("", C5)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M5" s="34" t="str">
-        <f t="shared" ref="M5" si="13">CONCATENATE("", D5)</f>
+        <f t="shared" ref="M5" si="12">CONCATENATE("", D5)</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N5" s="34" t="str">
-        <f t="shared" ref="N5" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N5" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
         <v>Motorizados</v>
       </c>
       <c r="O5" s="30" t="str">
@@ -2848,9 +2845,8 @@
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="W5" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>De.Motricidade</v>
+      <c r="W5" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X5" s="60" t="str">
         <f t="shared" si="6"/>
@@ -2859,20 +2855,23 @@
       <c r="Y5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z5" s="69" t="s">
+      <c r="Z5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="AB5" s="69" t="s">
+      <c r="AB5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD5" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="58">
         <v>6</v>
       </c>
@@ -2907,11 +2906,11 @@
         <v>9</v>
       </c>
       <c r="L6" s="34" t="str">
-        <f t="shared" ref="L6:M13" si="15">CONCATENATE("", C6)</f>
+        <f t="shared" ref="L6:M13" si="14">CONCATENATE("", C6)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M6" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N6" s="34" t="str">
@@ -2946,9 +2945,8 @@
         <f t="shared" si="5"/>
         <v>Maquinizados</v>
       </c>
-      <c r="W6" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>De.Motricidade</v>
+      <c r="W6" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X6" s="60" t="str">
         <f t="shared" si="6"/>
@@ -2957,20 +2955,23 @@
       <c r="Y6" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z6" s="69" t="s">
+      <c r="Z6" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="AB6" s="69" t="s">
+      <c r="AB6" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD6" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58">
         <v>7</v>
       </c>
@@ -3005,11 +3006,11 @@
         <v>9</v>
       </c>
       <c r="L7" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M7" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N7" s="34" t="str">
@@ -3044,9 +3045,8 @@
         <f t="shared" si="5"/>
         <v>Maquinizados</v>
       </c>
-      <c r="W7" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>De.Motricidade</v>
+      <c r="W7" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X7" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3055,20 +3055,23 @@
       <c r="Y7" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z7" s="69" t="s">
+      <c r="Z7" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="AB7" s="69" t="s">
+      <c r="AB7" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD7" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58">
         <v>8</v>
       </c>
@@ -3103,11 +3106,11 @@
         <v>9</v>
       </c>
       <c r="L8" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M8" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N8" s="34" t="str">
@@ -3142,9 +3145,8 @@
         <f t="shared" si="5"/>
         <v>Maquinizados</v>
       </c>
-      <c r="W8" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>De.Motricidade</v>
+      <c r="W8" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X8" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3153,20 +3155,23 @@
       <c r="Y8" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z8" s="69" t="s">
+      <c r="Z8" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="AB8" s="69" t="s">
+      <c r="AB8" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD8" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58">
         <v>9</v>
       </c>
@@ -3201,15 +3206,15 @@
         <v>9</v>
       </c>
       <c r="L9" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M9" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N9" s="34" t="str">
-        <f t="shared" ref="N9:N11" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N9:N11" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
         <v>Elevadores</v>
       </c>
       <c r="O9" s="30" t="str">
@@ -3229,20 +3234,19 @@
         <v>9</v>
       </c>
       <c r="T9" s="30" t="str">
-        <f t="shared" ref="T9:T14" si="17">SUBSTITUTE(C9, "_", " ")</f>
+        <f t="shared" ref="T9:T14" si="16">SUBSTITUTE(C9, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
       <c r="U9" s="30" t="str">
-        <f t="shared" ref="U9:U14" si="18">SUBSTITUTE(D9, "_", " ")</f>
+        <f t="shared" ref="U9:U14" si="17">SUBSTITUTE(D9, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="V9" s="30" t="str">
-        <f t="shared" ref="V9:V14" si="19">SUBSTITUTE(E9, "_", " ")</f>
+        <f t="shared" ref="V9:V14" si="18">SUBSTITUTE(E9, "_", " ")</f>
         <v>Elevadores</v>
       </c>
-      <c r="W9" s="30" t="str">
-        <f t="shared" ref="W9:W14" si="20">SUBSTITUTE(C9, "_", " ")</f>
-        <v>De.Motricidade</v>
+      <c r="W9" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X9" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3251,20 +3255,23 @@
       <c r="Y9" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z9" s="69" t="s">
+      <c r="Z9" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB9" s="69" t="s">
+      <c r="AB9" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD9" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58">
         <v>10</v>
       </c>
@@ -3299,19 +3306,19 @@
         <v>9</v>
       </c>
       <c r="L10" s="34" t="str">
+        <f t="shared" si="14"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="M10" s="34" t="str">
+        <f t="shared" si="14"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="N10" s="34" t="str">
         <f t="shared" si="15"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M10" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N10" s="34" t="str">
-        <f t="shared" si="16"/>
         <v>Elevadores</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f t="shared" ref="O10:O14" si="21">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),F10)</f>
+        <f t="shared" ref="O10:O14" si="19">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),F10)</f>
         <v>Elevador.MR</v>
       </c>
       <c r="P10" s="30" t="s">
@@ -3327,20 +3334,19 @@
         <v>9</v>
       </c>
       <c r="T10" s="30" t="str">
+        <f t="shared" si="16"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U10" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U10" s="30" t="str">
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V10" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V10" s="30" t="str">
-        <f t="shared" si="19"/>
         <v>Elevadores</v>
       </c>
-      <c r="W10" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De.Motricidade</v>
+      <c r="W10" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X10" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3349,20 +3355,23 @@
       <c r="Y10" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z10" s="69" t="s">
+      <c r="Z10" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB10" s="69" t="s">
+      <c r="AB10" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD10" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>11</v>
       </c>
@@ -3397,19 +3406,19 @@
         <v>9</v>
       </c>
       <c r="L11" s="34" t="str">
+        <f t="shared" si="14"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="M11" s="34" t="str">
+        <f t="shared" si="14"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="N11" s="34" t="str">
         <f t="shared" si="15"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M11" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N11" s="34" t="str">
-        <f t="shared" si="16"/>
         <v>Elevadores</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>Elevador.MRL</v>
       </c>
       <c r="P11" s="30" t="s">
@@ -3425,20 +3434,19 @@
         <v>9</v>
       </c>
       <c r="T11" s="30" t="str">
+        <f t="shared" si="16"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U11" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U11" s="30" t="str">
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V11" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V11" s="30" t="str">
-        <f t="shared" si="19"/>
         <v>Elevadores</v>
       </c>
-      <c r="W11" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De.Motricidade</v>
+      <c r="W11" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X11" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3447,20 +3455,23 @@
       <c r="Y11" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z11" s="69" t="s">
+      <c r="Z11" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB11" s="69" t="s">
+      <c r="AB11" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD11" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="58">
         <v>12</v>
       </c>
@@ -3495,11 +3506,11 @@
         <v>9</v>
       </c>
       <c r="L12" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M12" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N12" s="34" t="str">
@@ -3507,7 +3518,7 @@
         <v>Elevadores</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" ref="O12:O13" si="22">IF(ISNUMBER(FIND("Ifc",F12)),CONCATENATE("Classe IFC:   ",F12),F12)</f>
+        <f t="shared" ref="O12:O13" si="20">IF(ISNUMBER(FIND("Ifc",F12)),CONCATENATE("Classe IFC:   ",F12),F12)</f>
         <v>Plataforma</v>
       </c>
       <c r="P12" s="30" t="s">
@@ -3523,20 +3534,19 @@
         <v>9</v>
       </c>
       <c r="T12" s="30" t="str">
-        <f t="shared" ref="T12:T13" si="23">SUBSTITUTE(C12, "_", " ")</f>
+        <f t="shared" ref="T12:T13" si="21">SUBSTITUTE(C12, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
       <c r="U12" s="30" t="str">
-        <f t="shared" ref="U12:U13" si="24">SUBSTITUTE(D12, "_", " ")</f>
+        <f t="shared" ref="U12:U13" si="22">SUBSTITUTE(D12, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="V12" s="30" t="str">
-        <f t="shared" ref="V12:V13" si="25">SUBSTITUTE(E12, "_", " ")</f>
+        <f t="shared" ref="V12:V13" si="23">SUBSTITUTE(E12, "_", " ")</f>
         <v>Elevadores</v>
       </c>
-      <c r="W12" s="30" t="str">
-        <f t="shared" ref="W12:W13" si="26">SUBSTITUTE(C12, "_", " ")</f>
-        <v>De.Motricidade</v>
+      <c r="W12" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X12" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3545,20 +3555,23 @@
       <c r="Y12" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z12" s="69" t="s">
+      <c r="Z12" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB12" s="69" t="s">
+      <c r="AB12" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD12" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>13</v>
       </c>
@@ -3593,11 +3606,11 @@
         <v>9</v>
       </c>
       <c r="L13" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M13" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N13" s="34" t="str">
@@ -3605,7 +3618,7 @@
         <v>Elevadores</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>Plataforma.Articulada</v>
       </c>
       <c r="P13" s="30" t="s">
@@ -3621,20 +3634,19 @@
         <v>9</v>
       </c>
       <c r="T13" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U13" s="30" t="str">
+        <f t="shared" si="22"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V13" s="30" t="str">
         <f t="shared" si="23"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U13" s="30" t="str">
-        <f t="shared" si="24"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V13" s="30" t="str">
-        <f t="shared" si="25"/>
         <v>Elevadores</v>
       </c>
-      <c r="W13" s="30" t="str">
-        <f t="shared" si="26"/>
-        <v>De.Motricidade</v>
+      <c r="W13" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X13" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3643,20 +3655,23 @@
       <c r="Y13" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z13" s="69" t="s">
+      <c r="Z13" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB13" s="69" t="s">
+      <c r="AB13" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD13" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
         <v>14</v>
       </c>
@@ -3691,11 +3706,11 @@
         <v>9</v>
       </c>
       <c r="L14" s="34" t="str">
-        <f t="shared" ref="L14" si="27">CONCATENATE("", C14)</f>
+        <f t="shared" ref="L14" si="24">CONCATENATE("", C14)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M14" s="34" t="str">
-        <f t="shared" ref="M14" si="28">CONCATENATE("", D14)</f>
+        <f t="shared" ref="M14" si="25">CONCATENATE("", D14)</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N14" s="34" t="str">
@@ -3703,7 +3718,7 @@
         <v>Elevadores</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>Plataforma.Cesto</v>
       </c>
       <c r="P14" s="30" t="s">
@@ -3719,20 +3734,19 @@
         <v>9</v>
       </c>
       <c r="T14" s="30" t="str">
+        <f t="shared" si="16"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U14" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U14" s="30" t="str">
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V14" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V14" s="30" t="str">
-        <f t="shared" si="19"/>
         <v>Elevadores</v>
       </c>
-      <c r="W14" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De.Motricidade</v>
+      <c r="W14" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X14" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3741,20 +3755,23 @@
       <c r="Y14" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="Z14" s="69" t="s">
+      <c r="Z14" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB14" s="69" t="s">
+      <c r="AB14" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD14" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>15</v>
       </c>
@@ -3789,15 +3806,15 @@
         <v>9</v>
       </c>
       <c r="L15" s="34" t="str">
-        <f t="shared" ref="L15:M15" si="29">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:M15" si="26">CONCATENATE("", C15)</f>
         <v>De.Motricidade</v>
       </c>
       <c r="M15" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N15" s="34" t="str">
-        <f t="shared" ref="N15" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N15" si="27">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
         <v>Acessórios Motrizes</v>
       </c>
       <c r="O15" s="30" t="str">
@@ -3828,9 +3845,8 @@
         <f t="shared" si="5"/>
         <v>Acessórios.Motrizes</v>
       </c>
-      <c r="W15" s="30" t="str">
-        <f t="shared" si="11"/>
-        <v>De.Motricidade</v>
+      <c r="W15" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X15" s="60" t="str">
         <f t="shared" si="6"/>
@@ -3839,20 +3855,23 @@
       <c r="Y15" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z15" s="69" t="s">
+      <c r="Z15" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB15" s="69" t="s">
+      <c r="AB15" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD15" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="58">
         <v>16</v>
       </c>
@@ -3887,19 +3906,19 @@
         <v>9</v>
       </c>
       <c r="L16" s="34" t="str">
-        <f t="shared" ref="L16" si="31">CONCATENATE("", C16)</f>
+        <f t="shared" ref="L16" si="28">CONCATENATE("", C16)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M16" s="34" t="str">
-        <f t="shared" ref="M16" si="32">CONCATENATE("", D16)</f>
+        <f t="shared" ref="M16" si="29">CONCATENATE("", D16)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N16" s="34" t="str">
-        <f t="shared" ref="N16" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N16" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16" si="34">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
+        <f t="shared" ref="O16" si="31">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
         <v>Máquina</v>
       </c>
       <c r="P16" s="30" t="s">
@@ -3915,42 +3934,44 @@
         <v>9</v>
       </c>
       <c r="T16" s="30" t="str">
-        <f t="shared" ref="T16" si="35">SUBSTITUTE(C16, "_", " ")</f>
+        <f t="shared" ref="T16" si="32">SUBSTITUTE(C16, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="U16" s="30" t="str">
-        <f t="shared" ref="U16" si="36">SUBSTITUTE(D16, "_", " ")</f>
+        <f t="shared" ref="U16" si="33">SUBSTITUTE(D16, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
       <c r="V16" s="30" t="str">
-        <f t="shared" ref="V16" si="37">SUBSTITUTE(E16, "_", " ")</f>
+        <f t="shared" ref="V16" si="34">SUBSTITUTE(E16, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="W16" s="30" t="str">
-        <f t="shared" ref="W16" si="38">SUBSTITUTE(C16, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+      <c r="W16" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X16" s="60" t="str">
-        <f t="shared" ref="X16" si="39">CONCATENATE("Key-MOT-",A16)</f>
+        <f t="shared" ref="X16" si="35">CONCATENATE("Key-MOT-",A16)</f>
         <v>Key-MOT-16</v>
       </c>
       <c r="Y16" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z16" s="69" t="s">
+      <c r="Z16" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB16" s="69" t="s">
+      <c r="AB16" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD16" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58">
         <v>17</v>
       </c>
@@ -3985,19 +4006,19 @@
         <v>9</v>
       </c>
       <c r="L17" s="34" t="str">
-        <f t="shared" ref="L17:L18" si="40">CONCATENATE("", C17)</f>
+        <f t="shared" ref="L17:L18" si="36">CONCATENATE("", C17)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M17" s="34" t="str">
-        <f t="shared" ref="M17:M18" si="41">CONCATENATE("", D17)</f>
+        <f t="shared" ref="M17:M18" si="37">CONCATENATE("", D17)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N17" s="34" t="str">
-        <f t="shared" ref="N17:N18" si="42">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N17:N18" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" ref="O17:O18" si="43">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
+        <f t="shared" ref="O17:O18" si="39">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
         <v>Bomba</v>
       </c>
       <c r="P17" s="30" t="s">
@@ -4013,42 +4034,44 @@
         <v>9</v>
       </c>
       <c r="T17" s="30" t="str">
-        <f t="shared" ref="T17:T18" si="44">SUBSTITUTE(C17, "_", " ")</f>
+        <f t="shared" ref="T17:T18" si="40">SUBSTITUTE(C17, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="U17" s="30" t="str">
-        <f t="shared" ref="U17:U18" si="45">SUBSTITUTE(D17, "_", " ")</f>
+        <f t="shared" ref="U17:U18" si="41">SUBSTITUTE(D17, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
       <c r="V17" s="30" t="str">
-        <f t="shared" ref="V17:V18" si="46">SUBSTITUTE(E17, "_", " ")</f>
+        <f t="shared" ref="V17:V18" si="42">SUBSTITUTE(E17, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="W17" s="30" t="str">
-        <f t="shared" ref="W17:W18" si="47">SUBSTITUTE(C17, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+      <c r="W17" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X17" s="60" t="str">
-        <f t="shared" ref="X17:X18" si="48">CONCATENATE("Key-MOT-",A17)</f>
+        <f t="shared" ref="X17:X18" si="43">CONCATENATE("Key-MOT-",A17)</f>
         <v>Key-MOT-17</v>
       </c>
       <c r="Y17" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z17" s="69" t="s">
+      <c r="Z17" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB17" s="69" t="s">
+      <c r="AB17" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD17" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58">
         <v>18</v>
       </c>
@@ -4083,70 +4106,72 @@
         <v>9</v>
       </c>
       <c r="L18" s="34" t="str">
+        <f t="shared" si="36"/>
+        <v>De.Força.Motriz</v>
+      </c>
+      <c r="M18" s="34" t="str">
+        <f t="shared" si="37"/>
+        <v>Maquinárias</v>
+      </c>
+      <c r="N18" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>Máquinas</v>
+      </c>
+      <c r="O18" s="30" t="str">
+        <f t="shared" si="39"/>
+        <v>Motor</v>
+      </c>
+      <c r="P18" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q18" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="30" t="str">
         <f t="shared" si="40"/>
         <v>De.Força.Motriz</v>
       </c>
-      <c r="M18" s="34" t="str">
+      <c r="U18" s="30" t="str">
         <f t="shared" si="41"/>
         <v>Maquinárias</v>
       </c>
-      <c r="N18" s="34" t="str">
+      <c r="V18" s="30" t="str">
         <f t="shared" si="42"/>
         <v>Máquinas</v>
       </c>
-      <c r="O18" s="30" t="str">
+      <c r="W18" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X18" s="60" t="str">
         <f t="shared" si="43"/>
-        <v>Motor</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q18" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="R18" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="S18" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T18" s="30" t="str">
-        <f t="shared" si="44"/>
-        <v>De.Força.Motriz</v>
-      </c>
-      <c r="U18" s="30" t="str">
-        <f t="shared" si="45"/>
-        <v>Maquinárias</v>
-      </c>
-      <c r="V18" s="30" t="str">
-        <f t="shared" si="46"/>
-        <v>Máquinas</v>
-      </c>
-      <c r="W18" s="30" t="str">
-        <f t="shared" si="47"/>
-        <v>De.Força.Motriz</v>
-      </c>
-      <c r="X18" s="60" t="str">
-        <f t="shared" si="48"/>
         <v>Key-MOT-18</v>
       </c>
       <c r="Y18" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z18" s="69" t="s">
+      <c r="Z18" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB18" s="69" t="s">
+      <c r="AB18" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>19</v>
       </c>
@@ -4181,19 +4206,19 @@
         <v>9</v>
       </c>
       <c r="L19" s="34" t="str">
-        <f t="shared" ref="L19" si="49">CONCATENATE("", C19)</f>
+        <f t="shared" ref="L19" si="44">CONCATENATE("", C19)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M19" s="34" t="str">
-        <f t="shared" ref="M19" si="50">CONCATENATE("", D19)</f>
+        <f t="shared" ref="M19" si="45">CONCATENATE("", D19)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N19" s="34" t="str">
-        <f t="shared" ref="N19" si="51">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N19" si="46">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" ref="O19" si="52">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
+        <f t="shared" ref="O19" si="47">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
         <v>Elevador</v>
       </c>
       <c r="P19" s="30" t="s">
@@ -4209,42 +4234,44 @@
         <v>9</v>
       </c>
       <c r="T19" s="30" t="str">
-        <f t="shared" ref="T19" si="53">SUBSTITUTE(C19, "_", " ")</f>
+        <f t="shared" ref="T19" si="48">SUBSTITUTE(C19, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="U19" s="30" t="str">
-        <f t="shared" ref="U19" si="54">SUBSTITUTE(D19, "_", " ")</f>
+        <f t="shared" ref="U19" si="49">SUBSTITUTE(D19, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
       <c r="V19" s="30" t="str">
-        <f t="shared" ref="V19" si="55">SUBSTITUTE(E19, "_", " ")</f>
+        <f t="shared" ref="V19" si="50">SUBSTITUTE(E19, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="W19" s="30" t="str">
-        <f t="shared" ref="W19" si="56">SUBSTITUTE(C19, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+      <c r="W19" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X19" s="60" t="str">
-        <f t="shared" ref="X19" si="57">CONCATENATE("Key-MOT-",A19)</f>
+        <f t="shared" ref="X19" si="51">CONCATENATE("Key-MOT-",A19)</f>
         <v>Key-MOT-19</v>
       </c>
       <c r="Y19" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z19" s="69" t="s">
+      <c r="Z19" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB19" s="69" t="s">
+      <c r="AB19" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>20</v>
       </c>
@@ -4279,19 +4306,19 @@
         <v>9</v>
       </c>
       <c r="L20" s="34" t="str">
-        <f t="shared" ref="L20" si="58">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20" si="52">CONCATENATE("", C20)</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="M20" s="34" t="str">
-        <f t="shared" ref="M20" si="59">CONCATENATE("", D20)</f>
+        <f t="shared" ref="M20" si="53">CONCATENATE("", D20)</f>
         <v>Maquinárias</v>
       </c>
       <c r="N20" s="34" t="str">
-        <f t="shared" ref="N20" si="60">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N20" si="54">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
         <v>Máquinas</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" ref="O20" si="61">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
+        <f t="shared" ref="O20" si="55">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
         <v>Escada.Rolante</v>
       </c>
       <c r="P20" s="30" t="s">
@@ -4307,42 +4334,44 @@
         <v>9</v>
       </c>
       <c r="T20" s="30" t="str">
-        <f t="shared" ref="T20" si="62">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="T20" si="56">SUBSTITUTE(C20, "_", " ")</f>
         <v>De.Força.Motriz</v>
       </c>
       <c r="U20" s="30" t="str">
-        <f t="shared" ref="U20" si="63">SUBSTITUTE(D20, "_", " ")</f>
+        <f t="shared" ref="U20" si="57">SUBSTITUTE(D20, "_", " ")</f>
         <v>Maquinárias</v>
       </c>
       <c r="V20" s="30" t="str">
-        <f t="shared" ref="V20" si="64">SUBSTITUTE(E20, "_", " ")</f>
+        <f t="shared" ref="V20" si="58">SUBSTITUTE(E20, "_", " ")</f>
         <v>Máquinas</v>
       </c>
-      <c r="W20" s="30" t="str">
-        <f t="shared" ref="W20:W21" si="65">SUBSTITUTE(C20, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+      <c r="W20" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X20" s="60" t="str">
-        <f t="shared" ref="X20:X21" si="66">CONCATENATE("Key-MOT-",A20)</f>
+        <f t="shared" ref="X20" si="59">CONCATENATE("Key-MOT-",A20)</f>
         <v>Key-MOT-20</v>
       </c>
       <c r="Y20" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z20" s="69" t="s">
+      <c r="Z20" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB20" s="69" t="s">
+      <c r="AB20" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD20" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="58">
         <v>21</v>
       </c>
@@ -4377,68 +4406,468 @@
         <v>9</v>
       </c>
       <c r="L21" s="34" t="str">
-        <f t="shared" ref="L21:O21" si="67">SUBSTITUTE(CONCATENATE("", C21), ".", " ")</f>
+        <f t="shared" ref="L21:O25" si="60">SUBSTITUTE(CONCATENATE("", C21), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M21" s="34" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="60"/>
         <v>Macros</v>
       </c>
       <c r="N21" s="34" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="60"/>
         <v>Métodos</v>
       </c>
       <c r="O21" s="34" t="str">
-        <f t="shared" si="67"/>
-        <v>API Revit</v>
+        <f t="shared" si="60"/>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P21" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="Q21" s="67" t="str">
-        <f t="shared" ref="Q21" si="68">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Aplicación Revit</v>
-      </c>
-      <c r="R21" s="67" t="str">
-        <f t="shared" ref="R21" si="69">_xlfn.TRANSLATE(P21,"pt","en")</f>
-        <v>Revit App</v>
+      <c r="Q21" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="R21" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T21" s="30" t="str">
-        <f t="shared" ref="T21:V21" si="70">SUBSTITUTE(C21, ".", " ")</f>
+        <f t="shared" ref="T21:V25" si="61">SUBSTITUTE(C21, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U21" s="30" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
-      <c r="V21" s="68" t="str">
-        <f t="shared" si="70"/>
+      <c r="V21" s="67" t="str">
+        <f t="shared" si="61"/>
         <v>Métodos</v>
       </c>
-      <c r="W21" s="30" t="str">
-        <f t="shared" si="65"/>
-        <v>De.API</v>
+      <c r="W21" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="X21" s="60" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" ref="X21:X25" si="62">CONCATENATE("Key-MOT-",A21)</f>
         <v>Key-MOT-21</v>
       </c>
-      <c r="Y21" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z21" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA21" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB21" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC21" s="69" t="s">
+      <c r="Y21" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD21" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="58">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L22" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M22" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N22" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O22" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P22" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q22" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="R22" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="S22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T22" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U22" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V22" s="67" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W22" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X22" s="60" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-MOT-22</v>
+      </c>
+      <c r="Y22" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z22" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB22" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="58">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>228</v>
+      </c>
+      <c r="G23" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M23" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N23" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O23" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P23" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q23" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="R23" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="S23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U23" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V23" s="67" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W23" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X23" s="60" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-MOT-23</v>
+      </c>
+      <c r="Y23" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="58">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M24" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N24" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O24" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P24" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q24" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="R24" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="S24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T24" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U24" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V24" s="67" t="str">
+        <f t="shared" si="61"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W24" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X24" s="60" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-MOT-24</v>
+      </c>
+      <c r="Y24" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z24" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="58">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D25" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="G25" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M25" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N25" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O25" s="34" t="str">
+        <f t="shared" si="60"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P25" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q25" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="R25" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="S25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T25" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>De API</v>
+      </c>
+      <c r="U25" s="30" t="str">
+        <f t="shared" si="61"/>
+        <v>Macros</v>
+      </c>
+      <c r="V25" s="67" t="str">
+        <f t="shared" si="61"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W25" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X25" s="60" t="str">
+        <f t="shared" si="62"/>
+        <v>Key-MOT-25</v>
+      </c>
+      <c r="Y25" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z25" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD25" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4447,68 +4876,59 @@
     <sortCondition ref="F2:F740"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B21">
-    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B25">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 S1:Y1 AC1">
-    <cfRule type="cellIs" dxfId="34" priority="241" operator="equal">
+  <conditionalFormatting sqref="A1:O1 S1:Y1 AC1:AD1">
+    <cfRule type="cellIs" dxfId="27" priority="245" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F15:F20 F22:F1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="2020"/>
+  <conditionalFormatting sqref="E25:F25">
+    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F15:F20 F26:F1048576">
+    <cfRule type="duplicateValues" dxfId="25" priority="2024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="32" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="duplicateValues" dxfId="31" priority="2075"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2079"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:F8">
-    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F14">
-    <cfRule type="duplicateValues" dxfId="24" priority="2112"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F20 F22:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="2030"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="2036"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2037"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2038"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="2080"/>
+  <conditionalFormatting sqref="F15:F20 F26:F1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="2034"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2040"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2041"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2042"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2084"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F20">
-    <cfRule type="duplicateValues" dxfId="18" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="153"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q21">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+  <conditionalFormatting sqref="F21:F24">
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R14">
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R21">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y20">
-    <cfRule type="containsText" dxfId="7" priority="68" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="72" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4523,15 +4943,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -4596,7 +5016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -4679,15 +5099,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -4710,7 +5130,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -4766,30 +5186,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.53515625" customWidth="1"/>
-    <col min="4" max="4" width="7.53515625" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.69140625" customWidth="1"/>
-    <col min="8" max="8" width="6.69140625" customWidth="1"/>
-    <col min="9" max="9" width="11.84375" customWidth="1"/>
-    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.53515625" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="2.84375" customWidth="1"/>
-    <col min="14" max="14" width="7.3046875" customWidth="1"/>
-    <col min="15" max="15" width="13.84375" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -4848,7 +5268,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4907,7 +5327,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -4966,7 +5386,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -5025,7 +5445,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -5084,7 +5504,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -5143,7 +5563,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -5202,7 +5622,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -5261,7 +5681,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -5320,7 +5740,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>10</v>
       </c>

--- a/Versão5/SIS/Ontologia_Motriz.xlsx
+++ b/Versão5/SIS/Ontologia_Motriz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1C14B-CF9D-49F3-998D-ED61717EA1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FBC9AC-598D-4399-90EA-705E0D314A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="269">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -584,9 +584,6 @@
     <t>"Nome de um fabricante"</t>
   </si>
   <si>
-    <t>CTI_Projeto_A</t>
-  </si>
-  <si>
     <t>Conceitos</t>
   </si>
   <si>
@@ -596,9 +593,6 @@
     <t>Projeto</t>
   </si>
   <si>
-    <t>"Força motriz do Projeto Específico 01"</t>
-  </si>
-  <si>
     <t>[ MechanicalEquipment : OST_VerticalCirculation ]</t>
   </si>
   <si>
@@ -798,6 +792,93 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>De.Materialidade</t>
+  </si>
+  <si>
+    <t>Materialidades</t>
+  </si>
+  <si>
+    <t>Materiais</t>
+  </si>
+  <si>
+    <t>Mat.Cabo.de.Elétrica</t>
+  </si>
+  <si>
+    <t>Material usado em Cabo de Elétrica</t>
+  </si>
+  <si>
+    <t>Material utilizado en cables eléctricos</t>
+  </si>
+  <si>
+    <t>Material used in electrical cables</t>
+  </si>
+  <si>
+    <t>Instalações</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_WireMaterials ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial ]</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20 ]</t>
+  </si>
+  <si>
+    <t>Mat.Calha.de.Elétrica</t>
+  </si>
+  <si>
+    <t>Material usado em Calha de Elétrica</t>
+  </si>
+  <si>
+    <t>Material utilizado en canaletas eléctricas</t>
+  </si>
+  <si>
+    <t>Material used in electrical gutters</t>
+  </si>
+  <si>
+    <t>Mat.Canaleta.de.Elétrica</t>
+  </si>
+  <si>
+    <t>Material usado em Canaleta de Elétrica</t>
+  </si>
+  <si>
+    <t>Material utilizado en conductos eléctricos</t>
+  </si>
+  <si>
+    <t>Material used in electrical conduits</t>
+  </si>
+  <si>
+    <t>Mat.Eletroduto.Flexível</t>
+  </si>
+  <si>
+    <t>Material usado em Eletroduto Flexível</t>
+  </si>
+  <si>
+    <t>Material utilizado en conductos eléctricos flexibles</t>
+  </si>
+  <si>
+    <t>Material used in flexible electrical conduits</t>
+  </si>
+  <si>
+    <t>Mat.Eletroduto.Rígido</t>
+  </si>
+  <si>
+    <t>Material usado em Eletroduto Rígido</t>
+  </si>
+  <si>
+    <t>Material utilizado en conductos eléctricos rígidos</t>
+  </si>
+  <si>
+    <t>Material used in rigid electrical conduits</t>
+  </si>
+  <si>
+    <t>Projeto_FM</t>
+  </si>
+  <si>
+    <t>"Força motriz do Projeto Específico FM"</t>
   </si>
 </sst>
 </file>
@@ -1303,9 +1384,6 @@
     <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1350,12 +1428,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="34">
     <dxf>
       <font>
         <b val="0"/>
@@ -1418,6 +1499,14 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1618,11 +1707,53 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2065,14 +2196,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="47.140625" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="47.15234375" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2083,7 +2214,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2094,7 +2225,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2105,7 +2236,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2116,7 +2247,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2128,7 +2259,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2140,7 +2271,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2151,7 +2282,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="39" t="s">
         <v>54</v>
       </c>
@@ -2162,7 +2293,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2173,7 +2304,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2184,7 +2315,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2195,7 +2326,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2206,7 +2337,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2217,7 +2348,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2228,7 +2359,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2239,7 +2370,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2250,7 +2381,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2261,19 +2392,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46268.7008255787</v>
+        <v>46270.88739236111</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2284,7 +2415,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2295,7 +2426,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2306,7 +2437,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2317,7 +2448,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2328,7 +2459,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -2348,38 +2479,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AD25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD30"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.28515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.85546875" style="61" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.28515625" style="66" customWidth="1"/>
-    <col min="28" max="28" width="6" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="61"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.53515625" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46" style="60" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="44.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.84375" style="60" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.3046875" style="65" customWidth="1"/>
+    <col min="28" max="28" width="6" style="60" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="35.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="45" t="s">
         <v>90</v>
       </c>
@@ -2395,7 +2526,7 @@
       <c r="E1" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="55" t="s">
         <v>36</v>
       </c>
       <c r="G1" s="47" t="s">
@@ -2449,2487 +2580,2994 @@
       <c r="W1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="62" t="s">
+      <c r="X1" s="61" t="s">
         <v>8</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AA1" s="37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AC1" s="37" t="s">
         <v>82</v>
       </c>
       <c r="AD1" s="37" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="57">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="34" t="str">
+        <f t="shared" ref="L2:O6" si="0">SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M2" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N2" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O2" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Cabo de Elétrica</v>
+      </c>
+      <c r="P2" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="30" t="str">
+        <f t="shared" ref="T2:V6" si="1">SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U2" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V2" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W2" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="X2" s="59" t="str">
+        <f>CONCATENATE("Key-FMOT-",A2)</f>
+        <v>Key-FMOT-2</v>
+      </c>
+      <c r="Y2" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD2" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="G3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Calha de Elétrica</v>
+      </c>
+      <c r="P3" s="69" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="X3" s="59" t="str">
+        <f t="shared" ref="X3:X30" si="2">CONCATENATE("Key-FMOT-",A3)</f>
+        <v>Key-FMOT-3</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD3" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="57">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Canaleta de Elétrica</v>
+      </c>
+      <c r="P4" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W4" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="X4" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-4</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD4" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="57">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Eletroduto Flexível</v>
+      </c>
+      <c r="P5" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W5" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="X5" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-5</v>
+      </c>
+      <c r="Y5" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD5" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="57">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Eletroduto Rígido</v>
+      </c>
+      <c r="P6" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="X6" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-6</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD6" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="57">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="55" t="s">
+      <c r="D7" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="34" t="str">
-        <f t="shared" ref="L2:L4" si="0">CONCATENATE("", C2)</f>
+      <c r="G7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="34" t="str">
+        <f t="shared" ref="L7:L9" si="3">CONCATENATE("", C7)</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="M2" s="34" t="str">
-        <f t="shared" ref="M2:M4" si="1">CONCATENATE("", D2)</f>
+      <c r="M7" s="34" t="str">
+        <f t="shared" ref="M7:M9" si="4">CONCATENATE("", D7)</f>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="N2" s="34" t="str">
-        <f t="shared" ref="N2:N4" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+      <c r="N7" s="34" t="str">
+        <f t="shared" ref="N7:N9" si="5">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Motorizados</v>
       </c>
-      <c r="O2" s="30" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),F2)</f>
+      <c r="O7" s="30" t="str">
+        <f>IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),F7)</f>
         <v>Motor.de.Combustão</v>
       </c>
-      <c r="P2" s="30" t="s">
+      <c r="P7" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="Q2" s="30" t="s">
+      <c r="Q7" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="R2" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="S2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="30" t="str">
-        <f t="shared" ref="T2:T15" si="3">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R7" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="30" t="str">
+        <f t="shared" ref="T7:T20" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="U2" s="30" t="str">
-        <f t="shared" ref="U2:U15" si="4">SUBSTITUTE(D2, "_", " ")</f>
+      <c r="U7" s="30" t="str">
+        <f t="shared" ref="U7:U20" si="7">SUBSTITUTE(D7, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="V2" s="30" t="str">
-        <f t="shared" ref="V2:V15" si="5">SUBSTITUTE(E2, "_", " ")</f>
+      <c r="V7" s="30" t="str">
+        <f t="shared" ref="V7:V20" si="8">SUBSTITUTE(E7, "_", " ")</f>
         <v>Motorizados</v>
       </c>
-      <c r="W2" s="30" t="s">
+      <c r="W7" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X2" s="60" t="str">
-        <f t="shared" ref="X2:X15" si="6">CONCATENATE("Key-MOT-",A2)</f>
-        <v>Key-MOT-2</v>
-      </c>
-      <c r="Y2" s="30" t="s">
+      <c r="X7" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-7</v>
+      </c>
+      <c r="Y7" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="29" t="s">
+      <c r="Z7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AB2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="30" t="s">
+      <c r="AB7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="AD2" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="AD7" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="57">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="55" t="s">
+      <c r="D8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F8" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="34" t="str">
-        <f t="shared" ref="L3" si="7">CONCATENATE("", C3)</f>
+      <c r="G8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="34" t="str">
+        <f t="shared" ref="L8" si="9">CONCATENATE("", C8)</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="M3" s="34" t="str">
-        <f t="shared" ref="M3" si="8">CONCATENATE("", D3)</f>
+      <c r="M8" s="34" t="str">
+        <f t="shared" ref="M8" si="10">CONCATENATE("", D8)</f>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="N3" s="34" t="str">
-        <f t="shared" ref="N3" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+      <c r="N8" s="34" t="str">
+        <f t="shared" ref="N8" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
         <v>Motorizados</v>
       </c>
-      <c r="O3" s="30" t="str">
-        <f t="shared" ref="O3:O15" si="10">IF(ISNUMBER(FIND("Ifc",F3)),CONCATENATE("Classe IFC:   ",F3),F3)</f>
+      <c r="O8" s="30" t="str">
+        <f t="shared" ref="O8:O20" si="12">IF(ISNUMBER(FIND("Ifc",F8)),CONCATENATE("Classe IFC:   ",F8),F8)</f>
         <v>Motor.de.Acoplamento</v>
       </c>
-      <c r="P3" s="30" t="s">
+      <c r="P8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q3" s="30" t="s">
+      <c r="Q8" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="R3" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="30" t="str">
+      <c r="R8" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="30" t="str">
+        <f t="shared" si="6"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U8" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V8" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Motorizados</v>
+      </c>
+      <c r="W8" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X8" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-8</v>
+      </c>
+      <c r="Y8" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD8" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="57">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="34" t="str">
         <f t="shared" si="3"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="U3" s="30" t="str">
+      <c r="M9" s="34" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="V3" s="30" t="str">
+      <c r="N9" s="34" t="str">
         <f t="shared" si="5"/>
         <v>Motorizados</v>
       </c>
-      <c r="W3" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X3" s="60" t="str">
+      <c r="O9" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v>Motor.de.Acionamento.Correia</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Key-MOT-3</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD3" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="34" t="str">
-        <f t="shared" si="0"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="M4" s="34" t="str">
-        <f t="shared" si="1"/>
+      <c r="U9" s="30" t="str">
+        <f t="shared" si="7"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="N4" s="34" t="str">
-        <f t="shared" si="2"/>
+      <c r="V9" s="30" t="str">
+        <f t="shared" si="8"/>
         <v>Motorizados</v>
-      </c>
-      <c r="O4" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Motor.de.Acionamento.Correia</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q4" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="R4" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T4" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U4" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V4" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Motorizados</v>
-      </c>
-      <c r="W4" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X4" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-4</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC4" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD4" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="34" t="str">
-        <f t="shared" ref="L5" si="11">CONCATENATE("", C5)</f>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M5" s="34" t="str">
-        <f t="shared" ref="M5" si="12">CONCATENATE("", D5)</f>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N5" s="34" t="str">
-        <f t="shared" ref="N5" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E5),"."," ")," De "," de "))</f>
-        <v>Motorizados</v>
-      </c>
-      <c r="O5" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Motor.de.Acionamento.Direto</v>
-      </c>
-      <c r="P5" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="R5" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="S5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T5" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U5" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V5" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Motorizados</v>
-      </c>
-      <c r="W5" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X5" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-5</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD5" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="34" t="str">
-        <f t="shared" ref="L6:M13" si="14">CONCATENATE("", C6)</f>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M6" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N6" s="34" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
-        <v>Maquinizados</v>
-      </c>
-      <c r="O6" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Máquina.Motriz</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="R6" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="S6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T6" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U6" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V6" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Maquinizados</v>
-      </c>
-      <c r="W6" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X6" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-6</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD6" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="58">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F7" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M7" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N7" s="34" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
-        <v>Maquinizados</v>
-      </c>
-      <c r="O7" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Máquina.de.Combustão.Externa</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="R7" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T7" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U7" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V7" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Maquinizados</v>
-      </c>
-      <c r="W7" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X7" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-7</v>
-      </c>
-      <c r="Y7" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD7" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="58">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M8" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N8" s="34" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
-        <v>Maquinizados</v>
-      </c>
-      <c r="O8" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Máquina.de.Combustão.Interna</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="R8" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="S8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T8" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U8" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V8" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Maquinizados</v>
-      </c>
-      <c r="W8" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X8" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-8</v>
-      </c>
-      <c r="Y8" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC8" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD8" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="58">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M9" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N9" s="34" t="str">
-        <f t="shared" ref="N9:N11" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
-        <v>Elevadores</v>
-      </c>
-      <c r="O9" s="30" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F9)),CONCATENATE("Classe IFC:   ",F9),F9)</f>
-        <v>Elevador.Hidráulico</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T9" s="30" t="str">
-        <f t="shared" ref="T9:T14" si="16">SUBSTITUTE(C9, "_", " ")</f>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U9" s="30" t="str">
-        <f t="shared" ref="U9:U14" si="17">SUBSTITUTE(D9, "_", " ")</f>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V9" s="30" t="str">
-        <f t="shared" ref="V9:V14" si="18">SUBSTITUTE(E9, "_", " ")</f>
-        <v>Elevadores</v>
       </c>
       <c r="W9" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X9" s="60" t="str">
+      <c r="X9" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-9</v>
+      </c>
+      <c r="Y9" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD9" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="57">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="34" t="str">
+        <f t="shared" ref="L10" si="13">CONCATENATE("", C10)</f>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="M10" s="34" t="str">
+        <f t="shared" ref="M10" si="14">CONCATENATE("", D10)</f>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="N10" s="34" t="str">
+        <f t="shared" ref="N10" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E10),"."," ")," De "," de "))</f>
+        <v>Motorizados</v>
+      </c>
+      <c r="O10" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v>Motor.de.Acionamento.Direto</v>
+      </c>
+      <c r="P10" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q10" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="S10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Key-MOT-9</v>
-      </c>
-      <c r="Y9" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA9" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC9" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="AD9" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="58">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U10" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V10" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Motorizados</v>
+      </c>
+      <c r="W10" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X10" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-10</v>
+      </c>
+      <c r="Y10" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD10" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="57">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="G10" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="34" t="str">
-        <f t="shared" si="14"/>
+      <c r="D11" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="34" t="str">
+        <f t="shared" ref="L11:M18" si="16">CONCATENATE("", C11)</f>
         <v>De.Motricidade</v>
       </c>
-      <c r="M10" s="34" t="str">
-        <f t="shared" si="14"/>
+      <c r="M11" s="34" t="str">
+        <f t="shared" si="16"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="N10" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="O10" s="30" t="str">
-        <f t="shared" ref="O10:O14" si="19">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("Classe IFC:   ",F10),F10)</f>
-        <v>Elevador.MR</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q10" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="R10" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="S10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T10" s="30" t="str">
+      <c r="N11" s="34" t="str">
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <v>Maquinizados</v>
+      </c>
+      <c r="O11" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v>Máquina.Motriz</v>
+      </c>
+      <c r="P11" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q11" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="R11" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="30" t="str">
+        <f t="shared" si="6"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U11" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V11" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Maquinizados</v>
+      </c>
+      <c r="W11" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X11" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-11</v>
+      </c>
+      <c r="Y11" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD11" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="57">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="34" t="str">
         <f t="shared" si="16"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="U10" s="30" t="str">
-        <f t="shared" si="17"/>
+      <c r="M12" s="34" t="str">
+        <f t="shared" si="16"/>
         <v>Elementos.Motrizes</v>
       </c>
-      <c r="V10" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="W10" s="30" t="s">
+      <c r="N12" s="34" t="str">
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E12),"."," ")," De "," de "))</f>
+        <v>Maquinizados</v>
+      </c>
+      <c r="O12" s="30" t="str">
+        <f t="shared" si="12"/>
+        <v>Máquina.de.Combustão.Externa</v>
+      </c>
+      <c r="P12" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="S12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="30" t="str">
+        <f t="shared" si="6"/>
+        <v>De.Motricidade</v>
+      </c>
+      <c r="U12" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="V12" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>Maquinizados</v>
+      </c>
+      <c r="W12" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X10" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-10</v>
-      </c>
-      <c r="Y10" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA10" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC10" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="AD10" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="58">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="X12" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-12</v>
+      </c>
+      <c r="Y12" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD12" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="57">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F11" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="G11" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M11" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N11" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="O11" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Elevador.MRL</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q11" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="R11" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="S11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T11" s="30" t="str">
+      <c r="D13" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="34" t="str">
         <f t="shared" si="16"/>
         <v>De.Motricidade</v>
       </c>
-      <c r="U11" s="30" t="str">
-        <f t="shared" si="17"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V11" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Elevadores</v>
-      </c>
-      <c r="W11" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X11" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-11</v>
-      </c>
-      <c r="Y11" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA11" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC11" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="AD11" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="58">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G12" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M12" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N12" s="34" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E12),"."," ")," De "," de "))</f>
-        <v>Elevadores</v>
-      </c>
-      <c r="O12" s="30" t="str">
-        <f t="shared" ref="O12:O13" si="20">IF(ISNUMBER(FIND("Ifc",F12)),CONCATENATE("Classe IFC:   ",F12),F12)</f>
-        <v>Plataforma</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q12" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="R12" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="S12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T12" s="30" t="str">
-        <f t="shared" ref="T12:T13" si="21">SUBSTITUTE(C12, "_", " ")</f>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="U12" s="30" t="str">
-        <f t="shared" ref="U12:U13" si="22">SUBSTITUTE(D12, "_", " ")</f>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="V12" s="30" t="str">
-        <f t="shared" ref="V12:V13" si="23">SUBSTITUTE(E12, "_", " ")</f>
-        <v>Elevadores</v>
-      </c>
-      <c r="W12" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="X12" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-12</v>
-      </c>
-      <c r="Y12" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA12" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC12" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD12" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="58">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="G13" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v>De.Motricidade</v>
-      </c>
       <c r="M13" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N13" s="34" t="str">
         <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
-        <v>Elevadores</v>
+        <v>Maquinizados</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Plataforma.Articulada</v>
+        <f t="shared" si="12"/>
+        <v>Máquina.de.Combustão.Interna</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="S13" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T13" s="30" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>De.Motricidade</v>
       </c>
       <c r="U13" s="30" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="V13" s="30" t="str">
-        <f t="shared" si="23"/>
-        <v>Elevadores</v>
+        <f t="shared" si="8"/>
+        <v>Maquinizados</v>
       </c>
       <c r="W13" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X13" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-13</v>
+      <c r="X13" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-13</v>
       </c>
       <c r="Y13" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z13" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z13" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB13" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB13" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD13" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="58">
+        <v>144</v>
+      </c>
+      <c r="AD13" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="57">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>172</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="34" t="str">
-        <f t="shared" ref="L14" si="24">CONCATENATE("", C14)</f>
-        <v>De.Motricidade</v>
-      </c>
-      <c r="M14" s="34" t="str">
-        <f t="shared" ref="M14" si="25">CONCATENATE("", D14)</f>
-        <v>Elementos.Motrizes</v>
-      </c>
-      <c r="N14" s="34" t="str">
-        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E14),"."," ")," De "," de "))</f>
-        <v>Elevadores</v>
-      </c>
-      <c r="O14" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Plataforma.Cesto</v>
-      </c>
-      <c r="P14" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q14" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="R14" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="S14" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T14" s="30" t="str">
         <f t="shared" si="16"/>
         <v>De.Motricidade</v>
       </c>
+      <c r="M14" s="34" t="str">
+        <f t="shared" si="16"/>
+        <v>Elementos.Motrizes</v>
+      </c>
+      <c r="N14" s="34" t="str">
+        <f t="shared" ref="N14:N16" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E14),"."," ")," De "," de "))</f>
+        <v>Elevadores</v>
+      </c>
+      <c r="O14" s="30" t="str">
+        <f>IF(ISNUMBER(FIND("Ifc",F14)),CONCATENATE("Classe IFC:   ",F14),F14)</f>
+        <v>Elevador.Hidráulico</v>
+      </c>
+      <c r="P14" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q14" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="S14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="30" t="str">
+        <f t="shared" ref="T14:T19" si="18">SUBSTITUTE(C14, "_", " ")</f>
+        <v>De.Motricidade</v>
+      </c>
       <c r="U14" s="30" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="U14:U19" si="19">SUBSTITUTE(D14, "_", " ")</f>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="V14" s="30" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="V14:V19" si="20">SUBSTITUTE(E14, "_", " ")</f>
         <v>Elevadores</v>
       </c>
       <c r="W14" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X14" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-14</v>
+      <c r="X14" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-14</v>
       </c>
       <c r="Y14" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z14" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z14" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AB14" s="68" t="s">
+      <c r="AB14" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD14" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="58">
+        <v>164</v>
+      </c>
+      <c r="AD14" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="57">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>172</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="G15" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="34" t="str">
-        <f t="shared" ref="L15:M15" si="26">CONCATENATE("", C15)</f>
+        <f t="shared" si="16"/>
         <v>De.Motricidade</v>
       </c>
       <c r="M15" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="16"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="N15" s="34" t="str">
-        <f t="shared" ref="N15" si="27">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
-        <v>Acessórios Motrizes</v>
+        <f t="shared" si="17"/>
+        <v>Elevadores</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Acessório.Motriz</v>
+        <f t="shared" ref="O15:O19" si="21">IF(ISNUMBER(FIND("Ifc",F15)),CONCATENATE("Classe IFC:   ",F15),F15)</f>
+        <v>Elevador.MR</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="S15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T15" s="30" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="18"/>
         <v>De.Motricidade</v>
       </c>
       <c r="U15" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Motrizes</v>
       </c>
       <c r="V15" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Acessórios.Motrizes</v>
+        <f t="shared" si="20"/>
+        <v>Elevadores</v>
       </c>
       <c r="W15" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X15" s="60" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-MOT-15</v>
+      <c r="X15" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-15</v>
       </c>
       <c r="Y15" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z15" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z15" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB15" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB15" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD15" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="58">
+        <v>164</v>
+      </c>
+      <c r="AD15" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="57">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="G16" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="34" t="str">
-        <f t="shared" ref="L16" si="28">CONCATENATE("", C16)</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="16"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="M16" s="34" t="str">
-        <f t="shared" ref="M16" si="29">CONCATENATE("", D16)</f>
-        <v>Maquinárias</v>
+        <f t="shared" si="16"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="N16" s="34" t="str">
-        <f t="shared" ref="N16" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
-        <v>Máquinas</v>
+        <f t="shared" si="17"/>
+        <v>Elevadores</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16" si="31">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),F16)</f>
-        <v>Máquina</v>
+        <f t="shared" si="21"/>
+        <v>Elevador.MRL</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="S16" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T16" s="30" t="str">
-        <f t="shared" ref="T16" si="32">SUBSTITUTE(C16, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="18"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="U16" s="30" t="str">
-        <f t="shared" ref="U16" si="33">SUBSTITUTE(D16, "_", " ")</f>
-        <v>Maquinárias</v>
+        <f t="shared" si="19"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="V16" s="30" t="str">
-        <f t="shared" ref="V16" si="34">SUBSTITUTE(E16, "_", " ")</f>
-        <v>Máquinas</v>
+        <f t="shared" si="20"/>
+        <v>Elevadores</v>
       </c>
       <c r="W16" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X16" s="60" t="str">
-        <f t="shared" ref="X16" si="35">CONCATENATE("Key-MOT-",A16)</f>
-        <v>Key-MOT-16</v>
+      <c r="X16" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-16</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z16" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z16" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB16" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB16" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD16" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="58">
+        <v>164</v>
+      </c>
+      <c r="AD16" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="57">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E17" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="F17" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="G17" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="34" t="str">
-        <f t="shared" ref="L17:L18" si="36">CONCATENATE("", C17)</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="16"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="M17" s="34" t="str">
-        <f t="shared" ref="M17:M18" si="37">CONCATENATE("", D17)</f>
-        <v>Maquinárias</v>
+        <f t="shared" si="16"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="N17" s="34" t="str">
-        <f t="shared" ref="N17:N18" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
-        <v>Máquinas</v>
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E17),"."," ")," De "," de "))</f>
+        <v>Elevadores</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" ref="O17:O18" si="39">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
-        <v>Bomba</v>
+        <f t="shared" ref="O17:O18" si="22">IF(ISNUMBER(FIND("Ifc",F17)),CONCATENATE("Classe IFC:   ",F17),F17)</f>
+        <v>Plataforma</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="S17" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T17" s="30" t="str">
-        <f t="shared" ref="T17:T18" si="40">SUBSTITUTE(C17, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" ref="T17:T18" si="23">SUBSTITUTE(C17, "_", " ")</f>
+        <v>De.Motricidade</v>
       </c>
       <c r="U17" s="30" t="str">
-        <f t="shared" ref="U17:U18" si="41">SUBSTITUTE(D17, "_", " ")</f>
-        <v>Maquinárias</v>
+        <f t="shared" ref="U17:U18" si="24">SUBSTITUTE(D17, "_", " ")</f>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="V17" s="30" t="str">
-        <f t="shared" ref="V17:V18" si="42">SUBSTITUTE(E17, "_", " ")</f>
-        <v>Máquinas</v>
+        <f t="shared" ref="V17:V18" si="25">SUBSTITUTE(E17, "_", " ")</f>
+        <v>Elevadores</v>
       </c>
       <c r="W17" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X17" s="60" t="str">
-        <f t="shared" ref="X17:X18" si="43">CONCATENATE("Key-MOT-",A17)</f>
-        <v>Key-MOT-17</v>
+      <c r="X17" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-17</v>
       </c>
       <c r="Y17" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z17" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z17" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB17" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB17" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD17" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="58">
+        <v>165</v>
+      </c>
+      <c r="AD17" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="57">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="G18" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="34" t="str">
-        <f t="shared" si="36"/>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="16"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="M18" s="34" t="str">
-        <f t="shared" si="37"/>
-        <v>Maquinárias</v>
+        <f t="shared" si="16"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="N18" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v>Máquinas</v>
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
+        <v>Elevadores</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="39"/>
-        <v>Motor</v>
+        <f t="shared" si="22"/>
+        <v>Plataforma.Articulada</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T18" s="30" t="str">
-        <f t="shared" si="40"/>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="23"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="U18" s="30" t="str">
-        <f t="shared" si="41"/>
-        <v>Maquinárias</v>
+        <f t="shared" si="24"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="V18" s="30" t="str">
-        <f t="shared" si="42"/>
-        <v>Máquinas</v>
+        <f t="shared" si="25"/>
+        <v>Elevadores</v>
       </c>
       <c r="W18" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X18" s="60" t="str">
-        <f t="shared" si="43"/>
-        <v>Key-MOT-18</v>
+      <c r="X18" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-18</v>
       </c>
       <c r="Y18" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z18" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z18" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB18" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB18" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD18" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="58">
+        <v>165</v>
+      </c>
+      <c r="AD18" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="57">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E19" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="G19" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="34" t="str">
-        <f t="shared" ref="L19" si="44">CONCATENATE("", C19)</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" ref="L19" si="26">CONCATENATE("", C19)</f>
+        <v>De.Motricidade</v>
       </c>
       <c r="M19" s="34" t="str">
-        <f t="shared" ref="M19" si="45">CONCATENATE("", D19)</f>
-        <v>Maquinárias</v>
+        <f t="shared" ref="M19" si="27">CONCATENATE("", D19)</f>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="N19" s="34" t="str">
-        <f t="shared" ref="N19" si="46">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
-        <v>Máquinas</v>
+        <f>(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <v>Elevadores</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" ref="O19" si="47">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),F19)</f>
-        <v>Elevador</v>
+        <f t="shared" si="21"/>
+        <v>Plataforma.Cesto</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="S19" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T19" s="30" t="str">
-        <f t="shared" ref="T19" si="48">SUBSTITUTE(C19, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="18"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="U19" s="30" t="str">
-        <f t="shared" ref="U19" si="49">SUBSTITUTE(D19, "_", " ")</f>
-        <v>Maquinárias</v>
+        <f t="shared" si="19"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="V19" s="30" t="str">
-        <f t="shared" ref="V19" si="50">SUBSTITUTE(E19, "_", " ")</f>
-        <v>Máquinas</v>
+        <f t="shared" si="20"/>
+        <v>Elevadores</v>
       </c>
       <c r="W19" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X19" s="60" t="str">
-        <f t="shared" ref="X19" si="51">CONCATENATE("Key-MOT-",A19)</f>
-        <v>Key-MOT-19</v>
+      <c r="X19" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-19</v>
       </c>
       <c r="Y19" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z19" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z19" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB19" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB19" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD19" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="58">
+        <v>165</v>
+      </c>
+      <c r="AD19" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="57">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="G20" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="34" t="str">
-        <f t="shared" ref="L20" si="52">CONCATENATE("", C20)</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" ref="L20:M20" si="28">CONCATENATE("", C20)</f>
+        <v>De.Motricidade</v>
       </c>
       <c r="M20" s="34" t="str">
-        <f t="shared" ref="M20" si="53">CONCATENATE("", D20)</f>
-        <v>Maquinárias</v>
+        <f t="shared" si="28"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="N20" s="34" t="str">
-        <f t="shared" ref="N20" si="54">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
-        <v>Máquinas</v>
+        <f t="shared" ref="N20" si="29">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
+        <v>Acessórios Motrizes</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" ref="O20" si="55">IF(ISNUMBER(FIND("Ifc",F20)),CONCATENATE("Classe IFC:   ",F20),F20)</f>
-        <v>Escada.Rolante</v>
+        <f t="shared" si="12"/>
+        <v>Acessório.Motriz</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="S20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T20" s="30" t="str">
-        <f t="shared" ref="T20" si="56">SUBSTITUTE(C20, "_", " ")</f>
-        <v>De.Força.Motriz</v>
+        <f t="shared" si="6"/>
+        <v>De.Motricidade</v>
       </c>
       <c r="U20" s="30" t="str">
-        <f t="shared" ref="U20" si="57">SUBSTITUTE(D20, "_", " ")</f>
-        <v>Maquinárias</v>
+        <f t="shared" si="7"/>
+        <v>Elementos.Motrizes</v>
       </c>
       <c r="V20" s="30" t="str">
-        <f t="shared" ref="V20" si="58">SUBSTITUTE(E20, "_", " ")</f>
-        <v>Máquinas</v>
+        <f t="shared" si="8"/>
+        <v>Acessórios.Motrizes</v>
       </c>
       <c r="W20" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X20" s="60" t="str">
-        <f t="shared" ref="X20" si="59">CONCATENATE("Key-MOT-",A20)</f>
-        <v>Key-MOT-20</v>
+      <c r="X20" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-20</v>
       </c>
       <c r="Y20" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="Z20" s="68" t="s">
+      <c r="Z20" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB20" s="68" t="s">
+      <c r="AB20" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="AD20" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="58">
+      <c r="AD20" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="57">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="D21" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="E21" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="F21" s="63" t="s">
-        <v>220</v>
-      </c>
-      <c r="G21" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="34" t="str">
-        <f t="shared" ref="L21:O25" si="60">SUBSTITUTE(CONCATENATE("", C21), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="L21" si="30">CONCATENATE("", C21)</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="M21" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
+        <f t="shared" ref="M21" si="31">CONCATENATE("", D21)</f>
+        <v>Maquinárias</v>
       </c>
       <c r="N21" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O21" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Auxiliar</v>
+        <f t="shared" ref="N21" si="32">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E21),"."," ")," De "," de "))</f>
+        <v>Máquinas</v>
+      </c>
+      <c r="O21" s="30" t="str">
+        <f t="shared" ref="O21" si="33">IF(ISNUMBER(FIND("Ifc",F21)),CONCATENATE("Classe IFC:   ",F21),F21)</f>
+        <v>Máquina</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T21" s="30" t="str">
-        <f t="shared" ref="T21:V25" si="61">SUBSTITUTE(C21, ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="T21" si="34">SUBSTITUTE(C21, "_", " ")</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="U21" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V21" s="67" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <f t="shared" ref="U21" si="35">SUBSTITUTE(D21, "_", " ")</f>
+        <v>Maquinárias</v>
+      </c>
+      <c r="V21" s="30" t="str">
+        <f t="shared" ref="V21" si="36">SUBSTITUTE(E21, "_", " ")</f>
+        <v>Máquinas</v>
       </c>
       <c r="W21" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X21" s="60" t="str">
-        <f t="shared" ref="X21:X25" si="62">CONCATENATE("Key-MOT-",A21)</f>
-        <v>Key-MOT-21</v>
-      </c>
-      <c r="Y21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD21" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="58">
+      <c r="X21" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-21</v>
+      </c>
+      <c r="Y21" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD21" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="57">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="D22" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="E22" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="F22" s="63" t="s">
-        <v>224</v>
-      </c>
-      <c r="G22" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="G22" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
+        <f t="shared" ref="L22:L23" si="37">CONCATENATE("", C22)</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="M22" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
+        <f t="shared" ref="M22:M23" si="38">CONCATENATE("", D22)</f>
+        <v>Maquinárias</v>
       </c>
       <c r="N22" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O22" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Global</v>
+        <f t="shared" ref="N22:N23" si="39">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
+        <v>Máquinas</v>
+      </c>
+      <c r="O22" s="30" t="str">
+        <f t="shared" ref="O22:O23" si="40">IF(ISNUMBER(FIND("Ifc",F22)),CONCATENATE("Classe IFC:   ",F22),F22)</f>
+        <v>Bomba</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="S22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T22" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>De API</v>
+        <f t="shared" ref="T22:T23" si="41">SUBSTITUTE(C22, "_", " ")</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="U22" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V22" s="67" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <f t="shared" ref="U22:U23" si="42">SUBSTITUTE(D22, "_", " ")</f>
+        <v>Maquinárias</v>
+      </c>
+      <c r="V22" s="30" t="str">
+        <f t="shared" ref="V22:V23" si="43">SUBSTITUTE(E22, "_", " ")</f>
+        <v>Máquinas</v>
       </c>
       <c r="W22" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X22" s="60" t="str">
-        <f t="shared" si="62"/>
-        <v>Key-MOT-22</v>
-      </c>
-      <c r="Y22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD22" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="58">
+      <c r="X22" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-22</v>
+      </c>
+      <c r="Y22" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD22" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="57">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C23" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="E23" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="F23" s="63" t="s">
-        <v>228</v>
-      </c>
-      <c r="G23" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
+        <f t="shared" si="37"/>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="M23" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
+        <f t="shared" si="38"/>
+        <v>Maquinárias</v>
       </c>
       <c r="N23" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O23" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Local</v>
+        <f t="shared" si="39"/>
+        <v>Máquinas</v>
+      </c>
+      <c r="O23" s="30" t="str">
+        <f t="shared" si="40"/>
+        <v>Motor</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="S23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T23" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>De API</v>
+        <f t="shared" si="41"/>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="U23" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V23" s="67" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <f t="shared" si="42"/>
+        <v>Maquinárias</v>
+      </c>
+      <c r="V23" s="30" t="str">
+        <f t="shared" si="43"/>
+        <v>Máquinas</v>
       </c>
       <c r="W23" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X23" s="60" t="str">
-        <f t="shared" si="62"/>
-        <v>Key-MOT-23</v>
-      </c>
-      <c r="Y23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD23" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="58">
+      <c r="X23" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-23</v>
+      </c>
+      <c r="Y23" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD23" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="57">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="E24" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="F24" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="G24" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="G24" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
+        <f t="shared" ref="L24" si="44">CONCATENATE("", C24)</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="M24" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
+        <f t="shared" ref="M24" si="45">CONCATENATE("", D24)</f>
+        <v>Maquinárias</v>
       </c>
       <c r="N24" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O24" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Filtro</v>
+        <f t="shared" ref="N24" si="46">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <v>Máquinas</v>
+      </c>
+      <c r="O24" s="30" t="str">
+        <f t="shared" ref="O24" si="47">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),F24)</f>
+        <v>Elevador</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="S24" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T24" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>De API</v>
+        <f t="shared" ref="T24" si="48">SUBSTITUTE(C24, "_", " ")</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="U24" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V24" s="67" t="str">
-        <f t="shared" si="61"/>
-        <v>Métodos</v>
+        <f t="shared" ref="U24" si="49">SUBSTITUTE(D24, "_", " ")</f>
+        <v>Maquinárias</v>
+      </c>
+      <c r="V24" s="30" t="str">
+        <f t="shared" ref="V24" si="50">SUBSTITUTE(E24, "_", " ")</f>
+        <v>Máquinas</v>
       </c>
       <c r="W24" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X24" s="60" t="str">
-        <f t="shared" si="62"/>
-        <v>Key-MOT-24</v>
-      </c>
-      <c r="Y24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD24" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="58">
+      <c r="X24" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-24</v>
+      </c>
+      <c r="Y24" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD24" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="57">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="63" t="s">
-        <v>236</v>
-      </c>
-      <c r="F25" s="63" t="s">
-        <v>237</v>
-      </c>
-      <c r="G25" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
+        <f t="shared" ref="L25" si="51">CONCATENATE("", C25)</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="M25" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
+        <f t="shared" ref="M25" si="52">CONCATENATE("", D25)</f>
+        <v>Maquinárias</v>
       </c>
       <c r="N25" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O25" s="34" t="str">
-        <f t="shared" si="60"/>
-        <v>Bloco de Código</v>
+        <f t="shared" ref="N25" si="53">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E25),"."," ")," De "," de "))</f>
+        <v>Máquinas</v>
+      </c>
+      <c r="O25" s="30" t="str">
+        <f t="shared" ref="O25" si="54">IF(ISNUMBER(FIND("Ifc",F25)),CONCATENATE("Classe IFC:   ",F25),F25)</f>
+        <v>Escada.Rolante</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="S25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T25" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>De API</v>
+        <f t="shared" ref="T25" si="55">SUBSTITUTE(C25, "_", " ")</f>
+        <v>De.Força.Motriz</v>
       </c>
       <c r="U25" s="30" t="str">
-        <f t="shared" si="61"/>
-        <v>Macros</v>
-      </c>
-      <c r="V25" s="67" t="str">
-        <f t="shared" si="61"/>
-        <v>Códigos Visuais</v>
+        <f t="shared" ref="U25" si="56">SUBSTITUTE(D25, "_", " ")</f>
+        <v>Maquinárias</v>
+      </c>
+      <c r="V25" s="30" t="str">
+        <f t="shared" ref="V25" si="57">SUBSTITUTE(E25, "_", " ")</f>
+        <v>Máquinas</v>
       </c>
       <c r="W25" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="X25" s="60" t="str">
-        <f t="shared" si="62"/>
-        <v>Key-MOT-25</v>
-      </c>
-      <c r="Y25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD25" s="68" t="s">
+      <c r="X25" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-25</v>
+      </c>
+      <c r="Y25" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD25" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="57">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E26" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="34" t="str">
+        <f t="shared" ref="L26:O30" si="58">SUBSTITUTE(CONCATENATE("", C26), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M26" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Macros</v>
+      </c>
+      <c r="N26" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O26" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P26" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q26" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="R26" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="S26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="30" t="str">
+        <f t="shared" ref="T26:V30" si="59">SUBSTITUTE(C26, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U26" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>Macros</v>
+      </c>
+      <c r="V26" s="66" t="str">
+        <f t="shared" si="59"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W26" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X26" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-26</v>
+      </c>
+      <c r="Y26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="57">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E27" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>222</v>
+      </c>
+      <c r="G27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>De API</v>
+      </c>
+      <c r="M27" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Macros</v>
+      </c>
+      <c r="N27" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O27" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P27" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q27" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>De API</v>
+      </c>
+      <c r="U27" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>Macros</v>
+      </c>
+      <c r="V27" s="66" t="str">
+        <f t="shared" si="59"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W27" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X27" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-27</v>
+      </c>
+      <c r="Y27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="57">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="F28" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="G28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>De API</v>
+      </c>
+      <c r="M28" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Macros</v>
+      </c>
+      <c r="N28" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O28" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P28" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q28" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="R28" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="S28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T28" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>De API</v>
+      </c>
+      <c r="U28" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>Macros</v>
+      </c>
+      <c r="V28" s="66" t="str">
+        <f t="shared" si="59"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W28" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X28" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-28</v>
+      </c>
+      <c r="Y28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="57">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>230</v>
+      </c>
+      <c r="G29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>De API</v>
+      </c>
+      <c r="M29" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Macros</v>
+      </c>
+      <c r="N29" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O29" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P29" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>De API</v>
+      </c>
+      <c r="U29" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>Macros</v>
+      </c>
+      <c r="V29" s="66" t="str">
+        <f t="shared" si="59"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W29" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X29" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-29</v>
+      </c>
+      <c r="Y29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="57">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E30" s="62" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="G30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>De API</v>
+      </c>
+      <c r="M30" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Macros</v>
+      </c>
+      <c r="N30" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O30" s="34" t="str">
+        <f t="shared" si="58"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P30" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q30" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>De API</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" si="59"/>
+        <v>Macros</v>
+      </c>
+      <c r="V30" s="66" t="str">
+        <f t="shared" si="59"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W30" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="X30" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-FMOT-30</v>
+      </c>
+      <c r="Y30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="67" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC740">
-    <sortCondition ref="F2:F740"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AC745">
+    <sortCondition ref="F7:F745"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B25">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+  <conditionalFormatting sqref="A1:O1 S1:Y1 AC1:AD1">
+    <cfRule type="cellIs" dxfId="33" priority="251" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 S1:Y1 AC1:AD1">
-    <cfRule type="cellIs" dxfId="27" priority="245" operator="equal">
+  <conditionalFormatting sqref="E30:F30">
+    <cfRule type="duplicateValues" dxfId="32" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="31" priority="1687"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F10">
+    <cfRule type="duplicateValues" dxfId="25" priority="2085"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F13">
+    <cfRule type="duplicateValues" dxfId="24" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F19">
+    <cfRule type="duplicateValues" dxfId="18" priority="2122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F25 F1 F31:F1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="2030"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F25 F31:F1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="2040"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2046"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2047"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2048"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2090"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F25">
+    <cfRule type="duplicateValues" dxfId="11" priority="159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:F29">
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R19">
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E25:F25">
-    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F15:F20 F26:F1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="2024"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="24" priority="1681"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
-    <cfRule type="duplicateValues" dxfId="23" priority="2079"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F8">
-    <cfRule type="duplicateValues" dxfId="22" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F14">
-    <cfRule type="duplicateValues" dxfId="16" priority="2116"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F20 F26:F1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="2034"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2040"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2041"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="2042"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2084"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F20">
-    <cfRule type="duplicateValues" dxfId="10" priority="153"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
-    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
+  <conditionalFormatting sqref="Y2:Y6 AA2:AA6 AC2:AC6 A2:B30">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y20">
-    <cfRule type="containsText" dxfId="7" priority="72" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y2)))</formula>
+  <conditionalFormatting sqref="Y7:Y25">
+    <cfRule type="containsText" dxfId="7" priority="78" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4943,15 +5581,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5016,7 +5654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5099,15 +5737,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5130,7 +5768,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5186,30 +5824,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.53515625" customWidth="1"/>
+    <col min="5" max="5" width="5.921875" customWidth="1"/>
+    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.69140625" customWidth="1"/>
+    <col min="8" max="8" width="6.69140625" customWidth="1"/>
+    <col min="9" max="9" width="11.84375" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53515625" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="2.85546875" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.84375" customWidth="1"/>
+    <col min="14" max="14" width="7.3046875" customWidth="1"/>
+    <col min="15" max="15" width="13.84375" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.3046875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -5268,15 +5906,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>173</v>
+        <v>267</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>174</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>9</v>
@@ -5288,7 +5926,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="H2" s="51" t="s">
         <v>9</v>
@@ -5323,31 +5961,31 @@
       <c r="R2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="57" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S2" s="56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
       <c r="B3" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>178</v>
+      <c r="C3" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D3" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>166</v>
@@ -5382,31 +6020,31 @@
       <c r="R3" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S3" s="57" t="s">
+      <c r="S3" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
       <c r="B4" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="63" t="s">
-        <v>178</v>
+      <c r="C4" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D4" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H4" s="51" t="s">
         <v>166</v>
@@ -5441,31 +6079,31 @@
       <c r="R4" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S4" s="57" t="s">
+      <c r="S4" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
       <c r="B5" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="63" t="s">
-        <v>178</v>
+      <c r="C5" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D5" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H5" s="51" t="s">
         <v>166</v>
@@ -5500,31 +6138,31 @@
       <c r="R5" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S5" s="57" t="s">
+      <c r="S5" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
       <c r="B6" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="63" t="s">
-        <v>178</v>
+      <c r="C6" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D6" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H6" s="51" t="s">
         <v>166</v>
@@ -5559,31 +6197,31 @@
       <c r="R6" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S6" s="57" t="s">
+      <c r="S6" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
       <c r="B7" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="63" t="s">
-        <v>178</v>
+      <c r="C7" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D7" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H7" s="51" t="s">
         <v>166</v>
@@ -5618,31 +6256,31 @@
       <c r="R7" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="57" t="s">
+      <c r="S7" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="63" t="s">
-        <v>178</v>
+      <c r="C8" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D8" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H8" s="51" t="s">
         <v>166</v>
@@ -5677,31 +6315,31 @@
       <c r="R8" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S8" s="57" t="s">
+      <c r="S8" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
       <c r="B9" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="63" t="s">
-        <v>178</v>
+      <c r="C9" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H9" s="51" t="s">
         <v>166</v>
@@ -5736,31 +6374,31 @@
       <c r="R9" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S9" s="57" t="s">
+      <c r="S9" s="56" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>
       <c r="B10" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="63" t="s">
-        <v>178</v>
+      <c r="C10" s="62" t="s">
+        <v>176</v>
       </c>
       <c r="D10" s="52" t="s">
         <v>96</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H10" s="51" t="s">
         <v>166</v>
@@ -5795,7 +6433,7 @@
       <c r="R10" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="S10" s="57" t="s">
+      <c r="S10" s="56" t="s">
         <v>145</v>
       </c>
     </row>
